--- a/research/traditional_assets/database/data/brazil/brazil_diversified.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_diversified.xlsx
@@ -587,119 +587,122 @@
           <t>Diversified</t>
         </is>
       </c>
+      <c r="D2">
+        <v>-0.604</v>
+      </c>
       <c r="E2">
-        <v>0.225</v>
+        <v>-0.125</v>
       </c>
       <c r="G2">
-        <v>0.7219626168224299</v>
+        <v>-667.5</v>
       </c>
       <c r="H2">
-        <v>0.7219626168224299</v>
+        <v>-667.5</v>
       </c>
       <c r="I2">
-        <v>0.6705607476635514</v>
+        <v>-717.5</v>
       </c>
       <c r="J2">
-        <v>0.6010289183692947</v>
+        <v>-717.5</v>
       </c>
       <c r="K2">
-        <v>114.1</v>
+        <v>19.5</v>
       </c>
       <c r="L2">
-        <v>-2.66588785046729</v>
+        <v>2437.5</v>
       </c>
       <c r="M2">
-        <v>24.2</v>
+        <v>100.923</v>
       </c>
       <c r="N2">
-        <v>0.02788982367177596</v>
+        <v>0.09091343122241241</v>
       </c>
       <c r="O2">
-        <v>0.2120946538124452</v>
+        <v>5.175538461538461</v>
       </c>
       <c r="P2">
-        <v>24.2</v>
+        <v>100.9</v>
       </c>
       <c r="Q2">
-        <v>0.02788982367177596</v>
+        <v>0.09089271236825512</v>
       </c>
       <c r="R2">
-        <v>0.2120946538124452</v>
+        <v>5.174358974358975</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.02299999999999613</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.0002278965151649885</v>
       </c>
       <c r="U2">
-        <v>11.5</v>
+        <v>25.3</v>
       </c>
       <c r="V2">
-        <v>0.01325342860435634</v>
+        <v>0.02279073957301144</v>
       </c>
       <c r="W2">
-        <v>0.7203282828282828</v>
+        <v>0.07998359310910583</v>
       </c>
       <c r="X2">
-        <v>0.07559985125243054</v>
+        <v>0.1289744299837354</v>
       </c>
       <c r="Y2">
-        <v>0.6447284315758522</v>
+        <v>-0.0489908368746296</v>
       </c>
       <c r="Z2">
-        <v>-0.2341356673960612</v>
+        <v>2.583979328165375e-05</v>
       </c>
       <c r="AA2">
-        <v>-0.1407223069267276</v>
+        <v>-0.01854005167958656</v>
       </c>
       <c r="AB2">
-        <v>0.0720562552152982</v>
+        <v>0.1193986096516706</v>
       </c>
       <c r="AC2">
-        <v>-0.2127785621420258</v>
+        <v>-0.1379386613312572</v>
       </c>
       <c r="AD2">
-        <v>77.3</v>
+        <v>166.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>77.3</v>
+        <v>166.4</v>
       </c>
       <c r="AG2">
-        <v>65.8</v>
+        <v>141.1</v>
       </c>
       <c r="AH2">
-        <v>0.0817989417989418</v>
+        <v>0.1303564433999217</v>
       </c>
       <c r="AI2">
-        <v>0.2407349735284958</v>
+        <v>0.5211399937362982</v>
       </c>
       <c r="AJ2">
-        <v>0.07048741296197107</v>
+        <v>0.1127717391304348</v>
       </c>
       <c r="AK2">
-        <v>0.212532299741602</v>
+        <v>0.4799319727891156</v>
       </c>
       <c r="AL2">
-        <v>1.42</v>
+        <v>16.6</v>
       </c>
       <c r="AM2">
-        <v>-2.52</v>
+        <v>-1.099999999999998</v>
       </c>
       <c r="AN2">
-        <v>-2.684027777777778</v>
+        <v>-28.7392055267703</v>
       </c>
       <c r="AO2">
-        <v>-20.2112676056338</v>
+        <v>-0.3457831325301204</v>
       </c>
       <c r="AP2">
-        <v>-2.284722222222222</v>
+        <v>-24.36960276338515</v>
       </c>
       <c r="AQ2">
-        <v>11.38888888888889</v>
+        <v>5.218181818181828</v>
       </c>
     </row>
     <row r="3">
@@ -718,119 +721,122 @@
           <t>Diversified</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.604</v>
+      </c>
       <c r="E3">
-        <v>0.225</v>
+        <v>-0.125</v>
       </c>
       <c r="G3">
-        <v>0.7219626168224299</v>
+        <v>-667.5</v>
       </c>
       <c r="H3">
-        <v>0.7219626168224299</v>
+        <v>-667.5</v>
       </c>
       <c r="I3">
-        <v>0.6705607476635514</v>
+        <v>-717.5</v>
       </c>
       <c r="J3">
-        <v>0.6010289183692947</v>
+        <v>-717.5</v>
       </c>
       <c r="K3">
-        <v>114.1</v>
+        <v>19.5</v>
       </c>
       <c r="L3">
-        <v>-2.66588785046729</v>
+        <v>2437.5</v>
       </c>
       <c r="M3">
-        <v>24.2</v>
+        <v>100.923</v>
       </c>
       <c r="N3">
-        <v>0.02788982367177596</v>
+        <v>0.09091343122241241</v>
       </c>
       <c r="O3">
-        <v>0.2120946538124452</v>
+        <v>5.175538461538461</v>
       </c>
       <c r="P3">
-        <v>24.2</v>
+        <v>100.9</v>
       </c>
       <c r="Q3">
-        <v>0.02788982367177596</v>
+        <v>0.09089271236825512</v>
       </c>
       <c r="R3">
-        <v>0.2120946538124452</v>
+        <v>5.174358974358975</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.02299999999999613</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.0002278965151649885</v>
       </c>
       <c r="U3">
-        <v>11.5</v>
+        <v>25.3</v>
       </c>
       <c r="V3">
-        <v>0.01325342860435634</v>
+        <v>0.02279073957301144</v>
       </c>
       <c r="W3">
-        <v>0.7203282828282828</v>
+        <v>0.07998359310910583</v>
       </c>
       <c r="X3">
-        <v>0.07559985125243054</v>
+        <v>0.1289744299837354</v>
       </c>
       <c r="Y3">
-        <v>0.6447284315758522</v>
+        <v>-0.0489908368746296</v>
       </c>
       <c r="Z3">
-        <v>-0.2341356673960612</v>
+        <v>2.583979328165375e-05</v>
       </c>
       <c r="AA3">
-        <v>-0.1407223069267276</v>
+        <v>-0.01854005167958656</v>
       </c>
       <c r="AB3">
-        <v>0.0720562552152982</v>
+        <v>0.1193986096516706</v>
       </c>
       <c r="AC3">
-        <v>-0.2127785621420258</v>
+        <v>-0.1379386613312572</v>
       </c>
       <c r="AD3">
-        <v>77.3</v>
+        <v>166.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>77.3</v>
+        <v>166.4</v>
       </c>
       <c r="AG3">
-        <v>65.8</v>
+        <v>141.1</v>
       </c>
       <c r="AH3">
-        <v>0.0817989417989418</v>
+        <v>0.1303564433999217</v>
       </c>
       <c r="AI3">
-        <v>0.2407349735284958</v>
+        <v>0.5211399937362982</v>
       </c>
       <c r="AJ3">
-        <v>0.07048741296197107</v>
+        <v>0.1127717391304348</v>
       </c>
       <c r="AK3">
-        <v>0.212532299741602</v>
+        <v>0.4799319727891156</v>
       </c>
       <c r="AL3">
-        <v>1.42</v>
+        <v>16.6</v>
       </c>
       <c r="AM3">
-        <v>-2.52</v>
+        <v>-1.099999999999998</v>
       </c>
       <c r="AN3">
-        <v>-2.684027777777778</v>
+        <v>-28.7392055267703</v>
       </c>
       <c r="AO3">
-        <v>-20.2112676056338</v>
+        <v>-0.3457831325301204</v>
       </c>
       <c r="AP3">
-        <v>-2.284722222222222</v>
+        <v>-24.36960276338515</v>
       </c>
       <c r="AQ3">
-        <v>11.38888888888889</v>
+        <v>5.218181818181828</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/brazil/brazil_diversified.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_diversified.xlsx
@@ -1097,49 +1097,49 @@
         <v>0.0135502958579882</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>0.243010598594815</v>
       </c>
       <c r="G2">
         <v>418.581081081081</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>30.9527027027027</v>
       </c>
       <c r="I2">
         <v>0.135232481990832</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>792.3</v>
       </c>
       <c r="L2">
-        <v>896.739035204224</v>
+        <v>865.593867846636</v>
       </c>
       <c r="M2">
         <v>781.8</v>
       </c>
       <c r="N2">
-        <v>762.339035204224</v>
+        <v>740.355867846636</v>
       </c>
       <c r="O2">
         <v>123.9</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>9.162000000000001</v>
       </c>
       <c r="Q2">
         <v>0.100281823783756</v>
       </c>
       <c r="R2">
-        <v>0.101672633916391</v>
+        <v>0.103331643475761</v>
       </c>
       <c r="S2">
         <v>0.0545121092239028</v>
       </c>
       <c r="T2">
-        <v>0.033198</v>
+        <v>0.216317354289456</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1148,20 +1148,20 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="W2">
         <v>0.107439299025414</v>
       </c>
       <c r="X2">
-        <v>0.101672633916391</v>
+        <v>0.102190373669562</v>
       </c>
       <c r="Y2">
         <v>0.803366699813383</v>
       </c>
       <c r="Z2">
-        <v>0.728207721842937</v>
+        <v>0.7349556064464881</v>
       </c>
       <c r="AA2">
         <v>123.9</v>
@@ -1242,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1379,22 +1379,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1016726339163909</v>
+        <v>0.103331643475761</v>
       </c>
       <c r="C2">
-        <v>896.7390352042239</v>
+        <v>865.5938678466357</v>
       </c>
       <c r="D2">
-        <v>762.3390352042239</v>
+        <v>740.3558678466358</v>
       </c>
       <c r="E2">
-        <v>-123.9</v>
+        <v>-114.738</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9.161999999999999</v>
       </c>
       <c r="G2">
         <v>134.4</v>
@@ -1415,45 +1415,45 @@
         <v>0.525</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.1603996</v>
       </c>
       <c r="N2">
-        <v>0.525</v>
+        <v>-1.6353996</v>
       </c>
       <c r="O2">
-        <v>0.1785</v>
+        <v>-0.556035864</v>
       </c>
       <c r="P2">
-        <v>0.3465</v>
+        <v>-1.079363736</v>
       </c>
       <c r="Q2">
-        <v>0.4135</v>
+        <v>-1.012363736</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1016726339163909</v>
+        <v>0.102190373669562</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.7349556064464878</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
+        <v>0.2358</v>
       </c>
       <c r="V2">
-        <v>0.34</v>
+        <v>0.0826236035222373</v>
       </c>
       <c r="W2">
-        <v>0.03319799999999999</v>
+        <v>0.2163173542894564</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>0.2430105985948154</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1461,22 +1461,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.103331643475761</v>
+        <v>0.105231643475761</v>
       </c>
       <c r="C3">
-        <v>865.5938678466357</v>
+        <v>832.7630600089</v>
       </c>
       <c r="D3">
-        <v>740.3558678466358</v>
+        <v>716.6870600088999</v>
       </c>
       <c r="E3">
-        <v>-114.738</v>
+        <v>-105.576</v>
       </c>
       <c r="F3">
-        <v>9.161999999999999</v>
+        <v>18.324</v>
       </c>
       <c r="G3">
         <v>134.4</v>
@@ -1497,37 +1497,37 @@
         <v>0.525</v>
       </c>
       <c r="M3">
-        <v>2.1603996</v>
+        <v>4.3207992</v>
       </c>
       <c r="N3">
-        <v>-1.6353996</v>
+        <v>-3.7957992</v>
       </c>
       <c r="O3">
-        <v>-0.556035864</v>
+        <v>-1.290571728</v>
       </c>
       <c r="P3">
-        <v>-1.079363736</v>
+        <v>-2.505227472</v>
       </c>
       <c r="Q3">
-        <v>-1.012363736</v>
+        <v>-2.438227471999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.102190373669562</v>
+        <v>0.1027657856457821</v>
       </c>
       <c r="T3">
-        <v>0.7349556064464878</v>
+        <v>0.742455153451044</v>
       </c>
       <c r="U3">
         <v>0.2358</v>
       </c>
       <c r="V3">
-        <v>0.0826236035222373</v>
+        <v>0.04131180176111865</v>
       </c>
       <c r="W3">
-        <v>0.2163173542894564</v>
+        <v>0.2260586771447282</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>0.2430105985948154</v>
+        <v>0.1215052992974077</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1543,22 +1543,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.105231643475761</v>
+        <v>0.107131643475761</v>
       </c>
       <c r="C4">
-        <v>832.7630600089</v>
+        <v>801.3987295829255</v>
       </c>
       <c r="D4">
-        <v>716.6870600088999</v>
+        <v>694.4847295829255</v>
       </c>
       <c r="E4">
-        <v>-105.576</v>
+        <v>-96.41400000000002</v>
       </c>
       <c r="F4">
-        <v>18.324</v>
+        <v>27.486</v>
       </c>
       <c r="G4">
         <v>134.4</v>
@@ -1579,37 +1579,37 @@
         <v>0.525</v>
       </c>
       <c r="M4">
-        <v>4.3207992</v>
+        <v>6.4811988</v>
       </c>
       <c r="N4">
-        <v>-3.7957992</v>
+        <v>-5.956198799999999</v>
       </c>
       <c r="O4">
-        <v>-1.290571728</v>
+        <v>-2.025107592</v>
       </c>
       <c r="P4">
-        <v>-2.505227472</v>
+        <v>-3.931091207999999</v>
       </c>
       <c r="Q4">
-        <v>-2.438227471999999</v>
+        <v>-3.864091207999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1027657856457821</v>
+        <v>0.1033530617864602</v>
       </c>
       <c r="T4">
-        <v>0.742455153451044</v>
+        <v>0.7501093302907453</v>
       </c>
       <c r="U4">
         <v>0.2358</v>
       </c>
       <c r="V4">
-        <v>0.04131180176111865</v>
+        <v>0.0275412011740791</v>
       </c>
       <c r="W4">
-        <v>0.2260586771447282</v>
+        <v>0.2293057847631522</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>0.1215052992974077</v>
+        <v>0.08100353286493855</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.107131643475761</v>
+        <v>0.109031643475761</v>
       </c>
       <c r="C5">
-        <v>801.3987295829255</v>
+        <v>771.3686813451252</v>
       </c>
       <c r="D5">
-        <v>694.4847295829255</v>
+        <v>673.6166813451252</v>
       </c>
       <c r="E5">
-        <v>-96.41400000000002</v>
+        <v>-87.25200000000001</v>
       </c>
       <c r="F5">
-        <v>27.486</v>
+        <v>36.648</v>
       </c>
       <c r="G5">
         <v>134.4</v>
@@ -1661,37 +1661,37 @@
         <v>0.525</v>
       </c>
       <c r="M5">
-        <v>6.4811988</v>
+        <v>8.641598399999999</v>
       </c>
       <c r="N5">
-        <v>-5.956198799999999</v>
+        <v>-8.116598399999999</v>
       </c>
       <c r="O5">
-        <v>-2.025107592</v>
+        <v>-2.759643456</v>
       </c>
       <c r="P5">
-        <v>-3.931091207999999</v>
+        <v>-5.356954943999999</v>
       </c>
       <c r="Q5">
-        <v>-3.864091207999999</v>
+        <v>-5.289954943999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1033530617864602</v>
+        <v>0.1039525728467359</v>
       </c>
       <c r="T5">
-        <v>0.7501093302907453</v>
+        <v>0.7579229691479407</v>
       </c>
       <c r="U5">
         <v>0.2358</v>
       </c>
       <c r="V5">
-        <v>0.0275412011740791</v>
+        <v>0.02065590088055932</v>
       </c>
       <c r="W5">
-        <v>0.2293057847631522</v>
+        <v>0.2309293385723641</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>0.08100353286493855</v>
+        <v>0.06075264964870397</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.109031643475761</v>
+        <v>0.110931643475761</v>
       </c>
       <c r="C6">
-        <v>771.3686813451252</v>
+        <v>742.556145503326</v>
       </c>
       <c r="D6">
-        <v>673.6166813451252</v>
+        <v>653.9661455033259</v>
       </c>
       <c r="E6">
-        <v>-87.25200000000001</v>
+        <v>-78.09</v>
       </c>
       <c r="F6">
-        <v>36.648</v>
+        <v>45.81</v>
       </c>
       <c r="G6">
         <v>134.4</v>
@@ -1743,37 +1743,37 @@
         <v>0.525</v>
       </c>
       <c r="M6">
-        <v>8.641598399999999</v>
+        <v>10.801998</v>
       </c>
       <c r="N6">
-        <v>-8.116598399999999</v>
+        <v>-10.276998</v>
       </c>
       <c r="O6">
-        <v>-2.759643456</v>
+        <v>-3.494179320000001</v>
       </c>
       <c r="P6">
-        <v>-5.356954943999999</v>
+        <v>-6.78281868</v>
       </c>
       <c r="Q6">
-        <v>-5.289954943999999</v>
+        <v>-6.71581868</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1039525728467359</v>
+        <v>0.104564705192491</v>
       </c>
       <c r="T6">
-        <v>0.7579229691479407</v>
+        <v>0.7659011056652874</v>
       </c>
       <c r="U6">
         <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>0.02065590088055932</v>
+        <v>0.01652472070444745</v>
       </c>
       <c r="W6">
-        <v>0.2309293385723641</v>
+        <v>0.2319034708578913</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>0.06075264964870397</v>
+        <v>0.04860211971896311</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.110931643475761</v>
+        <v>0.112831643475761</v>
       </c>
       <c r="C7">
-        <v>742.556145503326</v>
+        <v>714.8575915412317</v>
       </c>
       <c r="D7">
-        <v>653.9661455033259</v>
+        <v>635.4295915412317</v>
       </c>
       <c r="E7">
-        <v>-78.09</v>
+        <v>-68.928</v>
       </c>
       <c r="F7">
-        <v>45.81</v>
+        <v>54.972</v>
       </c>
       <c r="G7">
         <v>134.4</v>
@@ -1825,37 +1825,37 @@
         <v>0.525</v>
       </c>
       <c r="M7">
-        <v>10.801998</v>
+        <v>12.9623976</v>
       </c>
       <c r="N7">
-        <v>-10.276998</v>
+        <v>-12.4373976</v>
       </c>
       <c r="O7">
-        <v>-3.494179320000001</v>
+        <v>-4.228715184</v>
       </c>
       <c r="P7">
-        <v>-6.78281868</v>
+        <v>-8.208682416</v>
       </c>
       <c r="Q7">
-        <v>-6.71581868</v>
+        <v>-8.141682416</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.104564705192491</v>
+        <v>0.105189861630709</v>
       </c>
       <c r="T7">
-        <v>0.7659011056652874</v>
+        <v>0.7740489897681095</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>0.01652472070444745</v>
+        <v>0.01377060058703955</v>
       </c>
       <c r="W7">
-        <v>0.2319034708578913</v>
+        <v>0.2325528923815761</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>0.04860211971896311</v>
+        <v>0.04050176643246928</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.112831643475761</v>
+        <v>0.114731643475761</v>
       </c>
       <c r="C8">
-        <v>714.8575915412317</v>
+        <v>688.1809036119805</v>
       </c>
       <c r="D8">
-        <v>635.4295915412317</v>
+        <v>617.9149036119805</v>
       </c>
       <c r="E8">
-        <v>-68.92800000000001</v>
+        <v>-59.76600000000002</v>
       </c>
       <c r="F8">
-        <v>54.97199999999999</v>
+        <v>64.13399999999999</v>
       </c>
       <c r="G8">
         <v>134.4</v>
@@ -1907,37 +1907,37 @@
         <v>0.525</v>
       </c>
       <c r="M8">
-        <v>12.9623976</v>
+        <v>15.1227972</v>
       </c>
       <c r="N8">
-        <v>-12.4373976</v>
+        <v>-14.5977972</v>
       </c>
       <c r="O8">
-        <v>-4.228715184</v>
+        <v>-4.963251047999999</v>
       </c>
       <c r="P8">
-        <v>-8.208682415999998</v>
+        <v>-9.634546151999999</v>
       </c>
       <c r="Q8">
-        <v>-8.141682415999998</v>
+        <v>-9.567546151999998</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.105189861630709</v>
+        <v>0.1058284622934048</v>
       </c>
       <c r="T8">
-        <v>0.7740489897681095</v>
+        <v>0.7823720971849709</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>0.01377060058703955</v>
+        <v>0.01180337193174819</v>
       </c>
       <c r="W8">
-        <v>0.2325528923815761</v>
+        <v>0.2330167648984938</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>0.04050176643246928</v>
+        <v>0.03471579979925943</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.114731643475761</v>
+        <v>0.116631643475761</v>
       </c>
       <c r="C9">
-        <v>688.1809036119806</v>
+        <v>662.4438495930162</v>
       </c>
       <c r="D9">
-        <v>617.9149036119807</v>
+        <v>601.3398495930162</v>
       </c>
       <c r="E9">
-        <v>-59.76600000000001</v>
+        <v>-50.60400000000001</v>
       </c>
       <c r="F9">
-        <v>64.134</v>
+        <v>73.29599999999999</v>
       </c>
       <c r="G9">
         <v>134.4</v>
@@ -1989,37 +1989,37 @@
         <v>0.525</v>
       </c>
       <c r="M9">
-        <v>15.1227972</v>
+        <v>17.2831968</v>
       </c>
       <c r="N9">
-        <v>-14.5977972</v>
+        <v>-16.7581968</v>
       </c>
       <c r="O9">
-        <v>-4.963251048000001</v>
+        <v>-5.697786912000001</v>
       </c>
       <c r="P9">
-        <v>-9.634546151999999</v>
+        <v>-11.060409888</v>
       </c>
       <c r="Q9">
-        <v>-9.567546151999998</v>
+        <v>-10.993409888</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1058284622934048</v>
+        <v>0.1064809455792026</v>
       </c>
       <c r="T9">
-        <v>0.7823720971849709</v>
+        <v>0.7908761417195901</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>0.01180337193174818</v>
+        <v>0.01032795044027966</v>
       </c>
       <c r="W9">
-        <v>0.2330167648984938</v>
+        <v>0.2333646692861821</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>0.03471579979925943</v>
+        <v>0.03037632482435182</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.116631643475761</v>
+        <v>0.118531643475761</v>
       </c>
       <c r="C10">
-        <v>662.4438495930162</v>
+        <v>637.5727901021841</v>
       </c>
       <c r="D10">
-        <v>601.3398495930162</v>
+        <v>585.6307901021841</v>
       </c>
       <c r="E10">
-        <v>-50.60400000000001</v>
+        <v>-41.44200000000002</v>
       </c>
       <c r="F10">
-        <v>73.29599999999999</v>
+        <v>82.45799999999998</v>
       </c>
       <c r="G10">
         <v>134.4</v>
@@ -2071,37 +2071,37 @@
         <v>0.525</v>
       </c>
       <c r="M10">
-        <v>17.2831968</v>
+        <v>19.4435964</v>
       </c>
       <c r="N10">
-        <v>-16.7581968</v>
+        <v>-18.9185964</v>
       </c>
       <c r="O10">
-        <v>-5.697786912000001</v>
+        <v>-6.432322776</v>
       </c>
       <c r="P10">
-        <v>-11.060409888</v>
+        <v>-12.486273624</v>
       </c>
       <c r="Q10">
-        <v>-10.993409888</v>
+        <v>-12.419273624</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1064809455792026</v>
+        <v>0.1071477691569961</v>
       </c>
       <c r="T10">
-        <v>0.7908761417195901</v>
+        <v>0.7995670883318934</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>0.01032795044027966</v>
+        <v>0.0091804003913597</v>
       </c>
       <c r="W10">
-        <v>0.2333646692861821</v>
+        <v>0.2336352615877174</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>0.03037632482435182</v>
+        <v>0.02700117762164611</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.118531643475761</v>
+        <v>0.120431643475761</v>
       </c>
       <c r="C11">
-        <v>637.5727901021841</v>
+        <v>613.5015847119056</v>
       </c>
       <c r="D11">
-        <v>585.6307901021841</v>
+        <v>570.7215847119056</v>
       </c>
       <c r="E11">
-        <v>-41.44200000000002</v>
+        <v>-32.28000000000002</v>
       </c>
       <c r="F11">
-        <v>82.45799999999998</v>
+        <v>91.61999999999999</v>
       </c>
       <c r="G11">
         <v>134.4</v>
@@ -2153,37 +2153,37 @@
         <v>0.525</v>
       </c>
       <c r="M11">
-        <v>19.4435964</v>
+        <v>21.603996</v>
       </c>
       <c r="N11">
-        <v>-18.9185964</v>
+        <v>-21.078996</v>
       </c>
       <c r="O11">
-        <v>-6.432322776</v>
+        <v>-7.166858640000001</v>
       </c>
       <c r="P11">
-        <v>-12.486273624</v>
+        <v>-13.91213736</v>
       </c>
       <c r="Q11">
-        <v>-12.419273624</v>
+        <v>-13.84513736</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1071477691569961</v>
+        <v>0.1078294110365182</v>
       </c>
       <c r="T11">
-        <v>0.7995670883318934</v>
+        <v>0.8084511670911366</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>0.0091804003913597</v>
+        <v>0.008262360352223729</v>
       </c>
       <c r="W11">
-        <v>0.2336352615877174</v>
+        <v>0.2338517354289457</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>0.02700117762164611</v>
+        <v>0.0243010598594815</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.120431643475761</v>
+        <v>0.122331643475761</v>
       </c>
       <c r="C12">
-        <v>613.5015847119056</v>
+        <v>590.1706610914941</v>
       </c>
       <c r="D12">
-        <v>570.7215847119056</v>
+        <v>556.5526610914942</v>
       </c>
       <c r="E12">
-        <v>-32.28</v>
+        <v>-23.11800000000001</v>
       </c>
       <c r="F12">
-        <v>91.62</v>
+        <v>100.782</v>
       </c>
       <c r="G12">
         <v>134.4</v>
@@ -2235,37 +2235,37 @@
         <v>0.525</v>
       </c>
       <c r="M12">
-        <v>21.603996</v>
+        <v>23.7643956</v>
       </c>
       <c r="N12">
-        <v>-21.078996</v>
+        <v>-23.2393956</v>
       </c>
       <c r="O12">
-        <v>-7.166858640000002</v>
+        <v>-7.901394504000002</v>
       </c>
       <c r="P12">
-        <v>-13.91213736</v>
+        <v>-15.338001096</v>
       </c>
       <c r="Q12">
-        <v>-13.84513736</v>
+        <v>-15.271001096</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1078294110365182</v>
+        <v>0.1085263707110859</v>
       </c>
       <c r="T12">
-        <v>0.8084511670911366</v>
+        <v>0.8175348880696888</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.008262360352223727</v>
+        <v>0.007511236683839752</v>
       </c>
       <c r="W12">
-        <v>0.2338517354289457</v>
+        <v>0.2340288503899506</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.0243010598594815</v>
+        <v>0.02209187259952861</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.122331643475761</v>
+        <v>0.124231643475761</v>
       </c>
       <c r="C13">
-        <v>590.1706610914941</v>
+        <v>567.5262194491661</v>
       </c>
       <c r="D13">
-        <v>556.5526610914942</v>
+        <v>543.0702194491661</v>
       </c>
       <c r="E13">
-        <v>-23.11800000000001</v>
+        <v>-13.95600000000002</v>
       </c>
       <c r="F13">
-        <v>100.782</v>
+        <v>109.944</v>
       </c>
       <c r="G13">
         <v>134.4</v>
@@ -2317,37 +2317,37 @@
         <v>0.525</v>
       </c>
       <c r="M13">
-        <v>23.7643956</v>
+        <v>25.9247952</v>
       </c>
       <c r="N13">
-        <v>-23.2393956</v>
+        <v>-25.3997952</v>
       </c>
       <c r="O13">
-        <v>-7.901394504000002</v>
+        <v>-8.635930368</v>
       </c>
       <c r="P13">
-        <v>-15.338001096</v>
+        <v>-16.763864832</v>
       </c>
       <c r="Q13">
-        <v>-15.271001096</v>
+        <v>-16.696864832</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1085263707110859</v>
+        <v>0.1092391703782573</v>
       </c>
       <c r="T13">
-        <v>0.8175348880696888</v>
+        <v>0.8268250572522987</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.007511236683839752</v>
+        <v>0.006885300293519774</v>
       </c>
       <c r="W13">
-        <v>0.2340288503899506</v>
+        <v>0.2341764461907881</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.02209187259952861</v>
+        <v>0.02025088321623458</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.124231643475761</v>
+        <v>0.126131643475761</v>
       </c>
       <c r="C14">
-        <v>567.5262194491661</v>
+        <v>545.5195498730385</v>
       </c>
       <c r="D14">
-        <v>543.0702194491661</v>
+        <v>530.2255498730385</v>
       </c>
       <c r="E14">
-        <v>-13.95600000000002</v>
+        <v>-4.794000000000011</v>
       </c>
       <c r="F14">
-        <v>109.944</v>
+        <v>119.106</v>
       </c>
       <c r="G14">
         <v>134.4</v>
@@ -2399,37 +2399,37 @@
         <v>0.525</v>
       </c>
       <c r="M14">
-        <v>25.9247952</v>
+        <v>28.0851948</v>
       </c>
       <c r="N14">
-        <v>-25.3997952</v>
+        <v>-27.5601948</v>
       </c>
       <c r="O14">
-        <v>-8.635930368</v>
+        <v>-9.370466232000002</v>
       </c>
       <c r="P14">
-        <v>-16.763864832</v>
+        <v>-18.189728568</v>
       </c>
       <c r="Q14">
-        <v>-16.696864832</v>
+        <v>-18.122728568</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1092391703782573</v>
+        <v>0.109968356244674</v>
       </c>
       <c r="T14">
-        <v>0.8268250572522987</v>
+        <v>0.8363287935425552</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.006885300293519774</v>
+        <v>0.006355661809402868</v>
       </c>
       <c r="W14">
-        <v>0.2341764461907881</v>
+        <v>0.2343013349453428</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.02025088321623458</v>
+        <v>0.01869312296883197</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.126131643475761</v>
+        <v>0.128031643475761</v>
       </c>
       <c r="C15">
-        <v>545.5195498730385</v>
+        <v>524.1064443110325</v>
       </c>
       <c r="D15">
-        <v>530.2255498730385</v>
+        <v>517.9744443110326</v>
       </c>
       <c r="E15">
-        <v>-4.794000000000011</v>
+        <v>4.367999999999995</v>
       </c>
       <c r="F15">
-        <v>119.106</v>
+        <v>128.268</v>
       </c>
       <c r="G15">
         <v>134.4</v>
@@ -2481,37 +2481,37 @@
         <v>0.525</v>
       </c>
       <c r="M15">
-        <v>28.0851948</v>
+        <v>30.2455944</v>
       </c>
       <c r="N15">
-        <v>-27.5601948</v>
+        <v>-29.7205944</v>
       </c>
       <c r="O15">
-        <v>-9.370466232000002</v>
+        <v>-10.105002096</v>
       </c>
       <c r="P15">
-        <v>-18.189728568</v>
+        <v>-19.615592304</v>
       </c>
       <c r="Q15">
-        <v>-18.122728568</v>
+        <v>-19.548592304</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.109968356244674</v>
+        <v>0.1107144999219377</v>
       </c>
       <c r="T15">
-        <v>0.8363287935425552</v>
+        <v>0.8460535469558407</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.006355661809402868</v>
+        <v>0.005901685965874091</v>
       </c>
       <c r="W15">
-        <v>0.2343013349453428</v>
+        <v>0.2344083824492469</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.01869312296883197</v>
+        <v>0.01735789989962966</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.128031643475761</v>
+        <v>0.129931643475761</v>
       </c>
       <c r="C16">
-        <v>524.1064443110325</v>
+        <v>503.2466882286319</v>
       </c>
       <c r="D16">
-        <v>517.9744443110326</v>
+        <v>506.2766882286319</v>
       </c>
       <c r="E16">
-        <v>4.367999999999995</v>
+        <v>13.53</v>
       </c>
       <c r="F16">
-        <v>128.268</v>
+        <v>137.43</v>
       </c>
       <c r="G16">
         <v>134.4</v>
@@ -2563,37 +2563,37 @@
         <v>0.525</v>
       </c>
       <c r="M16">
-        <v>30.2455944</v>
+        <v>32.405994</v>
       </c>
       <c r="N16">
-        <v>-29.7205944</v>
+        <v>-31.880994</v>
       </c>
       <c r="O16">
-        <v>-10.105002096</v>
+        <v>-10.83953796</v>
       </c>
       <c r="P16">
-        <v>-19.615592304</v>
+        <v>-21.04145604</v>
       </c>
       <c r="Q16">
-        <v>-19.548592304</v>
+        <v>-20.97445604</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1107144999219377</v>
+        <v>0.1114781999210193</v>
       </c>
       <c r="T16">
-        <v>0.8460535469558407</v>
+        <v>0.8560071180964977</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.005901685965874091</v>
+        <v>0.005508240234815819</v>
       </c>
       <c r="W16">
-        <v>0.2344083824492469</v>
+        <v>0.2345011569526305</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.01735789989962966</v>
+        <v>0.01620070657298767</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.129931643475761</v>
+        <v>0.131831643475761</v>
       </c>
       <c r="C17">
-        <v>503.2466882286321</v>
+        <v>482.9036196267585</v>
       </c>
       <c r="D17">
-        <v>506.2766882286321</v>
+        <v>495.0956196267585</v>
       </c>
       <c r="E17">
-        <v>13.52999999999997</v>
+        <v>22.69199999999998</v>
       </c>
       <c r="F17">
-        <v>137.43</v>
+        <v>146.592</v>
       </c>
       <c r="G17">
         <v>134.4</v>
@@ -2645,37 +2645,37 @@
         <v>0.525</v>
       </c>
       <c r="M17">
-        <v>32.405994</v>
+        <v>34.5663936</v>
       </c>
       <c r="N17">
-        <v>-31.880994</v>
+        <v>-34.0413936</v>
       </c>
       <c r="O17">
-        <v>-10.83953796</v>
+        <v>-11.574073824</v>
       </c>
       <c r="P17">
-        <v>-21.04145604</v>
+        <v>-22.467319776</v>
       </c>
       <c r="Q17">
-        <v>-20.97445604</v>
+        <v>-22.400319776</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1114781999210193</v>
+        <v>0.1122600832534124</v>
       </c>
       <c r="T17">
-        <v>0.8560071180964977</v>
+        <v>0.8661976790262179</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.005508240234815819</v>
+        <v>0.005163975220139831</v>
       </c>
       <c r="W17">
-        <v>0.2345011569526305</v>
+        <v>0.2345823346430911</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.01620070657298767</v>
+        <v>0.01518816241217591</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.131831643475761</v>
+        <v>0.133731643475761</v>
       </c>
       <c r="C18">
-        <v>482.9036196267585</v>
+        <v>463.0437452312896</v>
       </c>
       <c r="D18">
-        <v>495.0956196267585</v>
+        <v>484.3977452312896</v>
       </c>
       <c r="E18">
-        <v>22.69199999999998</v>
+        <v>31.85399999999998</v>
       </c>
       <c r="F18">
-        <v>146.592</v>
+        <v>155.754</v>
       </c>
       <c r="G18">
         <v>134.4</v>
@@ -2727,37 +2727,37 @@
         <v>0.525</v>
       </c>
       <c r="M18">
-        <v>34.5663936</v>
+        <v>36.7267932</v>
       </c>
       <c r="N18">
-        <v>-34.0413936</v>
+        <v>-36.2017932</v>
       </c>
       <c r="O18">
-        <v>-11.574073824</v>
+        <v>-12.308609688</v>
       </c>
       <c r="P18">
-        <v>-22.467319776</v>
+        <v>-23.893183512</v>
       </c>
       <c r="Q18">
-        <v>-22.400319776</v>
+        <v>-23.826183512</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1122600832534124</v>
+        <v>0.1130608071480318</v>
       </c>
       <c r="T18">
-        <v>0.8661976790262179</v>
+        <v>0.8766337956409916</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.005163975220139831</v>
+        <v>0.004860211971896311</v>
       </c>
       <c r="W18">
-        <v>0.2345823346430911</v>
+        <v>0.2346539620170268</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.01518816241217591</v>
+        <v>0.01429474109381268</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.133731643475761</v>
+        <v>0.135631643475761</v>
       </c>
       <c r="C19">
-        <v>463.0437452312896</v>
+        <v>443.6364053896804</v>
       </c>
       <c r="D19">
-        <v>484.3977452312896</v>
+        <v>474.1524053896804</v>
       </c>
       <c r="E19">
-        <v>31.85399999999998</v>
+        <v>41.01599999999999</v>
       </c>
       <c r="F19">
-        <v>155.754</v>
+        <v>164.916</v>
       </c>
       <c r="G19">
         <v>134.4</v>
@@ -2809,37 +2809,37 @@
         <v>0.525</v>
       </c>
       <c r="M19">
-        <v>36.7267932</v>
+        <v>38.8871928</v>
       </c>
       <c r="N19">
-        <v>-36.2017932</v>
+        <v>-38.3621928</v>
       </c>
       <c r="O19">
-        <v>-12.308609688</v>
+        <v>-13.043145552</v>
       </c>
       <c r="P19">
-        <v>-23.893183512</v>
+        <v>-25.319047248</v>
       </c>
       <c r="Q19">
-        <v>-23.826183512</v>
+        <v>-25.252047248</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1130608071480318</v>
+        <v>0.1138810608937395</v>
       </c>
       <c r="T19">
-        <v>0.8766337956409916</v>
+        <v>0.8873244516853939</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.004860211971896311</v>
+        <v>0.004590200195679849</v>
       </c>
       <c r="W19">
-        <v>0.2346539620170268</v>
+        <v>0.2347176307938587</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.01429474109381268</v>
+        <v>0.01350058881082306</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.135631643475761</v>
+        <v>0.137531643475761</v>
       </c>
       <c r="C20">
-        <v>443.6364053896805</v>
+        <v>424.6534806127419</v>
       </c>
       <c r="D20">
-        <v>474.1524053896804</v>
+        <v>464.3314806127418</v>
       </c>
       <c r="E20">
-        <v>41.01599999999996</v>
+        <v>50.178</v>
       </c>
       <c r="F20">
-        <v>164.916</v>
+        <v>174.078</v>
       </c>
       <c r="G20">
         <v>134.4</v>
@@ -2891,37 +2891,37 @@
         <v>0.525</v>
       </c>
       <c r="M20">
-        <v>38.88719279999999</v>
+        <v>41.0475924</v>
       </c>
       <c r="N20">
-        <v>-38.3621928</v>
+        <v>-40.5225924</v>
       </c>
       <c r="O20">
-        <v>-13.043145552</v>
+        <v>-13.777681416</v>
       </c>
       <c r="P20">
-        <v>-25.319047248</v>
+        <v>-26.744910984</v>
       </c>
       <c r="Q20">
-        <v>-25.252047248</v>
+        <v>-26.677910984</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1138810608937395</v>
+        <v>0.1147215678183536</v>
       </c>
       <c r="T20">
-        <v>0.8873244516853939</v>
+        <v>0.8982790745457074</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.00459020019567985</v>
+        <v>0.004348610711696699</v>
       </c>
       <c r="W20">
-        <v>0.2347176307938587</v>
+        <v>0.2347745975941819</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.01350058881082306</v>
+        <v>0.01279003150499025</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.137531643475761</v>
+        <v>0.139431643475761</v>
       </c>
       <c r="C21">
-        <v>424.6534806127419</v>
+        <v>406.0691338460465</v>
       </c>
       <c r="D21">
-        <v>464.3314806127418</v>
+        <v>454.9091338460465</v>
       </c>
       <c r="E21">
-        <v>50.178</v>
+        <v>59.34</v>
       </c>
       <c r="F21">
-        <v>174.078</v>
+        <v>183.24</v>
       </c>
       <c r="G21">
         <v>134.4</v>
@@ -2973,37 +2973,37 @@
         <v>0.525</v>
       </c>
       <c r="M21">
-        <v>41.0475924</v>
+        <v>43.207992</v>
       </c>
       <c r="N21">
-        <v>-40.5225924</v>
+        <v>-42.68299200000001</v>
       </c>
       <c r="O21">
-        <v>-13.777681416</v>
+        <v>-14.51221728</v>
       </c>
       <c r="P21">
-        <v>-26.744910984</v>
+        <v>-28.17077472</v>
       </c>
       <c r="Q21">
-        <v>-26.677910984</v>
+        <v>-28.10377472</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1147215678183536</v>
+        <v>0.115583087416083</v>
       </c>
       <c r="T21">
-        <v>0.8982790745457074</v>
+        <v>0.9095075629775288</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.004348610711696699</v>
+        <v>0.004131180176111864</v>
       </c>
       <c r="W21">
-        <v>0.2347745975941819</v>
+        <v>0.2348258677144728</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.01279003150499025</v>
+        <v>0.01215052992974075</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.139431643475761</v>
+        <v>0.141331643475761</v>
       </c>
       <c r="C22">
-        <v>406.0691338460465</v>
+        <v>387.8595834966505</v>
       </c>
       <c r="D22">
-        <v>454.9091338460465</v>
+        <v>445.8615834966506</v>
       </c>
       <c r="E22">
-        <v>59.34</v>
+        <v>68.50200000000001</v>
       </c>
       <c r="F22">
-        <v>183.24</v>
+        <v>192.402</v>
       </c>
       <c r="G22">
         <v>134.4</v>
@@ -3055,37 +3055,37 @@
         <v>0.525</v>
       </c>
       <c r="M22">
-        <v>43.207992</v>
+        <v>45.3683916</v>
       </c>
       <c r="N22">
-        <v>-42.68299200000001</v>
+        <v>-44.8433916</v>
       </c>
       <c r="O22">
-        <v>-14.51221728</v>
+        <v>-15.246753144</v>
       </c>
       <c r="P22">
-        <v>-28.17077472</v>
+        <v>-29.596638456</v>
       </c>
       <c r="Q22">
-        <v>-28.10377472</v>
+        <v>-29.529638456</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.115583087416083</v>
+        <v>0.1164664176365398</v>
       </c>
       <c r="T22">
-        <v>0.9095075629775288</v>
+        <v>0.9210203169392696</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.004131180176111864</v>
+        <v>0.003934457310582728</v>
       </c>
       <c r="W22">
-        <v>0.2348258677144728</v>
+        <v>0.2348722549661646</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.01215052992974075</v>
+        <v>0.01157193326641981</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.141331643475761</v>
+        <v>0.143231643475761</v>
       </c>
       <c r="C23">
-        <v>387.8595834966506</v>
+        <v>370.0029030168495</v>
       </c>
       <c r="D23">
-        <v>445.8615834966506</v>
+        <v>437.1669030168494</v>
       </c>
       <c r="E23">
-        <v>68.50199999999998</v>
+        <v>77.66399999999999</v>
       </c>
       <c r="F23">
-        <v>192.402</v>
+        <v>201.564</v>
       </c>
       <c r="G23">
         <v>134.4</v>
@@ -3137,37 +3137,37 @@
         <v>0.525</v>
       </c>
       <c r="M23">
-        <v>45.3683916</v>
+        <v>47.5287912</v>
       </c>
       <c r="N23">
-        <v>-44.8433916</v>
+        <v>-47.0037912</v>
       </c>
       <c r="O23">
-        <v>-15.246753144</v>
+        <v>-15.981289008</v>
       </c>
       <c r="P23">
-        <v>-29.596638456</v>
+        <v>-31.022502192</v>
       </c>
       <c r="Q23">
-        <v>-29.529638456</v>
+        <v>-30.955502192</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1164664176365398</v>
+        <v>0.1173723973498287</v>
       </c>
       <c r="T23">
-        <v>0.9210203169392696</v>
+        <v>0.9328282697205422</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.003934457310582729</v>
+        <v>0.003755618341919876</v>
       </c>
       <c r="W23">
-        <v>0.2348722549661646</v>
+        <v>0.2349144251949753</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.01157193326641981</v>
+        <v>0.01104593629976436</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.143231643475761</v>
+        <v>0.145131643475761</v>
       </c>
       <c r="C24">
-        <v>370.0029030168495</v>
+        <v>352.478843489115</v>
       </c>
       <c r="D24">
-        <v>437.1669030168494</v>
+        <v>428.8048434891149</v>
       </c>
       <c r="E24">
-        <v>77.66399999999999</v>
+        <v>86.82599999999999</v>
       </c>
       <c r="F24">
-        <v>201.564</v>
+        <v>210.726</v>
       </c>
       <c r="G24">
         <v>134.4</v>
@@ -3219,37 +3219,37 @@
         <v>0.525</v>
       </c>
       <c r="M24">
-        <v>47.5287912</v>
+        <v>49.6891908</v>
       </c>
       <c r="N24">
-        <v>-47.0037912</v>
+        <v>-49.1641908</v>
       </c>
       <c r="O24">
-        <v>-15.981289008</v>
+        <v>-16.715824872</v>
       </c>
       <c r="P24">
-        <v>-31.022502192</v>
+        <v>-32.448365928</v>
       </c>
       <c r="Q24">
-        <v>-30.955502192</v>
+        <v>-32.381365928</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1173723973498287</v>
+        <v>0.1183019090037226</v>
       </c>
       <c r="T24">
-        <v>0.9328282697205422</v>
+        <v>0.9449429225740558</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.003755618341919876</v>
+        <v>0.00359233058792336</v>
       </c>
       <c r="W24">
-        <v>0.2349144251949753</v>
+        <v>0.2349529284473677</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.01104593629976436</v>
+        <v>0.01056567819977461</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.145131643475761</v>
+        <v>0.147031643475761</v>
       </c>
       <c r="C25">
-        <v>352.478843489115</v>
+        <v>335.2686761902761</v>
       </c>
       <c r="D25">
-        <v>428.8048434891149</v>
+        <v>420.7566761902762</v>
       </c>
       <c r="E25">
-        <v>86.82599999999999</v>
+        <v>95.988</v>
       </c>
       <c r="F25">
-        <v>210.726</v>
+        <v>219.888</v>
       </c>
       <c r="G25">
         <v>134.4</v>
@@ -3301,37 +3301,37 @@
         <v>0.525</v>
       </c>
       <c r="M25">
-        <v>49.6891908</v>
+        <v>51.8495904</v>
       </c>
       <c r="N25">
-        <v>-49.1641908</v>
+        <v>-51.32459040000001</v>
       </c>
       <c r="O25">
-        <v>-16.715824872</v>
+        <v>-17.450360736</v>
       </c>
       <c r="P25">
-        <v>-32.448365928</v>
+        <v>-33.874229664</v>
       </c>
       <c r="Q25">
-        <v>-32.381365928</v>
+        <v>-33.807229664</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1183019090037226</v>
+        <v>0.1192558814906137</v>
       </c>
       <c r="T25">
-        <v>0.9449429225740558</v>
+        <v>0.9573763820816092</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.00359233058792336</v>
+        <v>0.003442650146759887</v>
       </c>
       <c r="W25">
-        <v>0.2349529284473677</v>
+        <v>0.234988223095394</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.01056567819977461</v>
+        <v>0.01012544160811724</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.147031643475761</v>
+        <v>0.148931643475761</v>
       </c>
       <c r="C26">
-        <v>335.2686761902762</v>
+        <v>318.3550525583944</v>
       </c>
       <c r="D26">
-        <v>420.7566761902762</v>
+        <v>413.0050525583944</v>
       </c>
       <c r="E26">
-        <v>95.98799999999997</v>
+        <v>105.15</v>
       </c>
       <c r="F26">
-        <v>219.888</v>
+        <v>229.05</v>
       </c>
       <c r="G26">
         <v>134.4</v>
@@ -3383,37 +3383,37 @@
         <v>0.525</v>
       </c>
       <c r="M26">
-        <v>51.8495904</v>
+        <v>54.00998999999999</v>
       </c>
       <c r="N26">
-        <v>-51.3245904</v>
+        <v>-53.48499</v>
       </c>
       <c r="O26">
-        <v>-17.450360736</v>
+        <v>-18.1848966</v>
       </c>
       <c r="P26">
-        <v>-33.874229664</v>
+        <v>-35.30009339999999</v>
       </c>
       <c r="Q26">
-        <v>-33.807229664</v>
+        <v>-35.23309339999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1192558814906137</v>
+        <v>0.1202352932438219</v>
       </c>
       <c r="T26">
-        <v>0.9573763820816091</v>
+        <v>0.9701414005093639</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.003442650146759887</v>
+        <v>0.003304944140889492</v>
       </c>
       <c r="W26">
-        <v>0.234988223095394</v>
+        <v>0.2350206941715783</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.01012544160811724</v>
+        <v>0.009720423943792578</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.148931643475761</v>
+        <v>0.150831643475761</v>
       </c>
       <c r="C27">
-        <v>318.3550525583944</v>
+        <v>301.7218793586526</v>
       </c>
       <c r="D27">
-        <v>413.0050525583944</v>
+        <v>405.5338793586526</v>
       </c>
       <c r="E27">
-        <v>105.15</v>
+        <v>114.312</v>
       </c>
       <c r="F27">
-        <v>229.05</v>
+        <v>238.212</v>
       </c>
       <c r="G27">
         <v>134.4</v>
@@ -3465,37 +3465,37 @@
         <v>0.525</v>
       </c>
       <c r="M27">
-        <v>54.00998999999999</v>
+        <v>56.1703896</v>
       </c>
       <c r="N27">
-        <v>-53.48499</v>
+        <v>-55.6453896</v>
       </c>
       <c r="O27">
-        <v>-18.1848966</v>
+        <v>-18.919432464</v>
       </c>
       <c r="P27">
-        <v>-35.30009339999999</v>
+        <v>-36.725957136</v>
       </c>
       <c r="Q27">
-        <v>-35.23309339999999</v>
+        <v>-36.658957136</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1202352932438219</v>
+        <v>0.1212411755849546</v>
       </c>
       <c r="T27">
-        <v>0.9701414005093639</v>
+        <v>0.9832514194351661</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.003304944140889492</v>
+        <v>0.003177830904701434</v>
       </c>
       <c r="W27">
-        <v>0.2350206941715783</v>
+        <v>0.2350506674726714</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.009720423943792578</v>
+        <v>0.009346561484415927</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.150831643475761</v>
+        <v>0.152731643475761</v>
       </c>
       <c r="C28">
-        <v>301.7218793586526</v>
+        <v>285.3542071578311</v>
       </c>
       <c r="D28">
-        <v>405.5338793586526</v>
+        <v>398.3282071578311</v>
       </c>
       <c r="E28">
-        <v>114.312</v>
+        <v>123.474</v>
       </c>
       <c r="F28">
-        <v>238.212</v>
+        <v>247.374</v>
       </c>
       <c r="G28">
         <v>134.4</v>
@@ -3547,37 +3547,37 @@
         <v>0.525</v>
       </c>
       <c r="M28">
-        <v>56.1703896</v>
+        <v>58.3307892</v>
       </c>
       <c r="N28">
-        <v>-55.6453896</v>
+        <v>-57.8057892</v>
       </c>
       <c r="O28">
-        <v>-18.919432464</v>
+        <v>-19.653968328</v>
       </c>
       <c r="P28">
-        <v>-36.725957136</v>
+        <v>-38.151820872</v>
       </c>
       <c r="Q28">
-        <v>-36.658957136</v>
+        <v>-38.084820872</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1212411755849546</v>
+        <v>0.1222746163463924</v>
       </c>
       <c r="T28">
-        <v>0.9832514194351661</v>
+        <v>0.9967206169616755</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.003177830904701434</v>
+        <v>0.003060133463786566</v>
       </c>
       <c r="W28">
-        <v>0.2350506674726714</v>
+        <v>0.2350784205292391</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.009346561484415927</v>
+        <v>0.009000392540548741</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.152731643475761</v>
+        <v>0.154631643475761</v>
       </c>
       <c r="C29">
-        <v>285.3542071578311</v>
+        <v>269.2381304809641</v>
       </c>
       <c r="D29">
-        <v>398.3282071578311</v>
+        <v>391.3741304809641</v>
       </c>
       <c r="E29">
-        <v>123.474</v>
+        <v>132.636</v>
       </c>
       <c r="F29">
-        <v>247.374</v>
+        <v>256.536</v>
       </c>
       <c r="G29">
         <v>134.4</v>
@@ -3629,37 +3629,37 @@
         <v>0.525</v>
       </c>
       <c r="M29">
-        <v>58.3307892</v>
+        <v>60.4911888</v>
       </c>
       <c r="N29">
-        <v>-57.8057892</v>
+        <v>-59.9661888</v>
       </c>
       <c r="O29">
-        <v>-19.653968328</v>
+        <v>-20.388504192</v>
       </c>
       <c r="P29">
-        <v>-38.151820872</v>
+        <v>-39.577684608</v>
       </c>
       <c r="Q29">
-        <v>-38.084820872</v>
+        <v>-39.510684608</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1222746163463924</v>
+        <v>0.1233367637956478</v>
       </c>
       <c r="T29">
-        <v>0.9967206169616755</v>
+        <v>1.010563958863921</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.003060133463786566</v>
+        <v>0.002950842982937046</v>
       </c>
       <c r="W29">
-        <v>0.2350784205292391</v>
+        <v>0.2351041912246234</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.009000392540548741</v>
+        <v>0.008678949949814774</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.154631643475761</v>
+        <v>0.156531643475761</v>
       </c>
       <c r="C30">
-        <v>269.2381304809641</v>
+        <v>253.3606982470281</v>
       </c>
       <c r="D30">
-        <v>391.3741304809641</v>
+        <v>384.6586982470282</v>
       </c>
       <c r="E30">
-        <v>132.636</v>
+        <v>141.798</v>
       </c>
       <c r="F30">
-        <v>256.536</v>
+        <v>265.698</v>
       </c>
       <c r="G30">
         <v>134.4</v>
@@ -3711,37 +3711,37 @@
         <v>0.525</v>
       </c>
       <c r="M30">
-        <v>60.4911888</v>
+        <v>62.65158840000001</v>
       </c>
       <c r="N30">
-        <v>-59.9661888</v>
+        <v>-62.12658840000001</v>
       </c>
       <c r="O30">
-        <v>-20.388504192</v>
+        <v>-21.123040056</v>
       </c>
       <c r="P30">
-        <v>-39.577684608</v>
+        <v>-41.00354834400001</v>
       </c>
       <c r="Q30">
-        <v>-39.510684608</v>
+        <v>-40.93654834400001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1233367637956478</v>
+        <v>0.1244288308913612</v>
       </c>
       <c r="T30">
-        <v>1.010563958863921</v>
+        <v>1.024797254059187</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.002950842982937046</v>
+        <v>0.002849089776628871</v>
       </c>
       <c r="W30">
-        <v>0.2351041912246234</v>
+        <v>0.2351281846306709</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.008678949949814774</v>
+        <v>0.008379675813614318</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.156531643475761</v>
+        <v>0.158431643475761</v>
       </c>
       <c r="C31">
-        <v>253.3606982470283</v>
+        <v>237.7098332698725</v>
       </c>
       <c r="D31">
-        <v>384.6586982470282</v>
+        <v>378.1698332698725</v>
       </c>
       <c r="E31">
-        <v>141.798</v>
+        <v>150.96</v>
       </c>
       <c r="F31">
-        <v>265.698</v>
+        <v>274.86</v>
       </c>
       <c r="G31">
         <v>134.4</v>
@@ -3793,37 +3793,37 @@
         <v>0.525</v>
       </c>
       <c r="M31">
-        <v>62.65158839999999</v>
+        <v>64.811988</v>
       </c>
       <c r="N31">
-        <v>-62.1265884</v>
+        <v>-64.28698799999999</v>
       </c>
       <c r="O31">
-        <v>-21.123040056</v>
+        <v>-21.85757592</v>
       </c>
       <c r="P31">
-        <v>-41.003548344</v>
+        <v>-42.42941207999999</v>
       </c>
       <c r="Q31">
-        <v>-40.93654834399999</v>
+        <v>-42.36241207999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1244288308913612</v>
+        <v>0.1255520999040949</v>
       </c>
       <c r="T31">
-        <v>1.024797254059187</v>
+        <v>1.039437214831461</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.002849089776628872</v>
+        <v>0.002754120117407909</v>
       </c>
       <c r="W31">
-        <v>0.2351281846306709</v>
+        <v>0.2351505784763152</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.008379675813614318</v>
+        <v>0.008100353286493944</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.158431643475761</v>
+        <v>0.160331643475761</v>
       </c>
       <c r="C32">
-        <v>237.7098332698725</v>
+        <v>222.2742597716905</v>
       </c>
       <c r="D32">
-        <v>378.1698332698725</v>
+        <v>371.8962597716906</v>
       </c>
       <c r="E32">
-        <v>150.96</v>
+        <v>160.122</v>
       </c>
       <c r="F32">
-        <v>274.86</v>
+        <v>284.022</v>
       </c>
       <c r="G32">
         <v>134.4</v>
@@ -3875,37 +3875,37 @@
         <v>0.525</v>
       </c>
       <c r="M32">
-        <v>64.811988</v>
+        <v>66.9723876</v>
       </c>
       <c r="N32">
-        <v>-64.28698799999999</v>
+        <v>-66.4473876</v>
       </c>
       <c r="O32">
-        <v>-21.85757592</v>
+        <v>-22.592111784</v>
       </c>
       <c r="P32">
-        <v>-42.42941207999999</v>
+        <v>-43.855275816</v>
       </c>
       <c r="Q32">
-        <v>-42.36241207999999</v>
+        <v>-43.788275816</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1255520999040949</v>
+        <v>0.1267079274389369</v>
       </c>
       <c r="T32">
-        <v>1.039437214831461</v>
+        <v>1.054501522292787</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.002754120117407909</v>
+        <v>0.002665277532975396</v>
       </c>
       <c r="W32">
-        <v>0.2351505784763152</v>
+        <v>0.2351715275577244</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.008100353286493944</v>
+        <v>0.007839051567574806</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.160331643475761</v>
+        <v>0.162231643475761</v>
       </c>
       <c r="C33">
-        <v>222.2742597716905</v>
+        <v>207.0434379937577</v>
       </c>
       <c r="D33">
-        <v>371.8962597716906</v>
+        <v>365.8274379937577</v>
       </c>
       <c r="E33">
-        <v>160.122</v>
+        <v>169.284</v>
       </c>
       <c r="F33">
-        <v>284.022</v>
+        <v>293.184</v>
       </c>
       <c r="G33">
         <v>134.4</v>
@@ -3957,37 +3957,37 @@
         <v>0.525</v>
       </c>
       <c r="M33">
-        <v>66.9723876</v>
+        <v>69.1327872</v>
       </c>
       <c r="N33">
-        <v>-66.4473876</v>
+        <v>-68.60778719999999</v>
       </c>
       <c r="O33">
-        <v>-22.592111784</v>
+        <v>-23.326647648</v>
       </c>
       <c r="P33">
-        <v>-43.855275816</v>
+        <v>-45.28113955199999</v>
       </c>
       <c r="Q33">
-        <v>-43.788275816</v>
+        <v>-45.21413955199999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1267079274389369</v>
+        <v>0.1278977499012742</v>
       </c>
       <c r="T33">
-        <v>1.054501522292787</v>
+        <v>1.070008897620622</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.002665277532975396</v>
+        <v>0.002581987610069916</v>
       </c>
       <c r="W33">
-        <v>0.2351715275577244</v>
+        <v>0.2351911673215455</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.007839051567574806</v>
+        <v>0.007594081206088066</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.162231643475761</v>
+        <v>0.164131643475761</v>
       </c>
       <c r="C34">
-        <v>207.0434379937577</v>
+        <v>192.0075051067315</v>
       </c>
       <c r="D34">
-        <v>365.8274379937577</v>
+        <v>359.9535051067315</v>
       </c>
       <c r="E34">
-        <v>169.284</v>
+        <v>178.446</v>
       </c>
       <c r="F34">
-        <v>293.184</v>
+        <v>302.346</v>
       </c>
       <c r="G34">
         <v>134.4</v>
@@ -4039,37 +4039,37 @@
         <v>0.525</v>
       </c>
       <c r="M34">
-        <v>69.1327872</v>
+        <v>71.2931868</v>
       </c>
       <c r="N34">
-        <v>-68.60778719999999</v>
+        <v>-70.7681868</v>
       </c>
       <c r="O34">
-        <v>-23.326647648</v>
+        <v>-24.061183512</v>
       </c>
       <c r="P34">
-        <v>-45.28113955199999</v>
+        <v>-46.707003288</v>
       </c>
       <c r="Q34">
-        <v>-45.21413955199999</v>
+        <v>-46.640003288</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1278977499012742</v>
+        <v>0.1291230894520394</v>
       </c>
       <c r="T34">
-        <v>1.070008897620622</v>
+        <v>1.085979179674661</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.002581987610069916</v>
+        <v>0.002503745561279918</v>
       </c>
       <c r="W34">
-        <v>0.2351911673215455</v>
+        <v>0.2352096167966502</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.007594081206088066</v>
+        <v>0.007363957533176313</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.164131643475761</v>
+        <v>0.166031643475761</v>
       </c>
       <c r="C35">
-        <v>192.0075051067315</v>
+        <v>177.1572217236579</v>
       </c>
       <c r="D35">
-        <v>359.9535051067315</v>
+        <v>354.2652217236579</v>
       </c>
       <c r="E35">
-        <v>178.446</v>
+        <v>187.608</v>
       </c>
       <c r="F35">
-        <v>302.346</v>
+        <v>311.508</v>
       </c>
       <c r="G35">
         <v>134.4</v>
@@ -4121,37 +4121,37 @@
         <v>0.525</v>
       </c>
       <c r="M35">
-        <v>71.2931868</v>
+        <v>73.45358639999999</v>
       </c>
       <c r="N35">
-        <v>-70.7681868</v>
+        <v>-72.92858639999999</v>
       </c>
       <c r="O35">
-        <v>-24.061183512</v>
+        <v>-24.795719376</v>
       </c>
       <c r="P35">
-        <v>-46.707003288</v>
+        <v>-48.13286702399999</v>
       </c>
       <c r="Q35">
-        <v>-46.640003288</v>
+        <v>-48.06586702399999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1291230894520394</v>
+        <v>0.1303855605043431</v>
       </c>
       <c r="T35">
-        <v>1.085979179674661</v>
+        <v>1.102433409669732</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.002503745561279918</v>
+        <v>0.002430105985948156</v>
       </c>
       <c r="W35">
-        <v>0.2352096167966502</v>
+        <v>0.2352269810085134</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.007363957533176313</v>
+        <v>0.007147370546906395</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.166031643475761</v>
+        <v>0.167931643475761</v>
       </c>
       <c r="C36">
-        <v>177.1572217236579</v>
+        <v>162.4839234055563</v>
       </c>
       <c r="D36">
-        <v>354.2652217236579</v>
+        <v>348.7539234055563</v>
       </c>
       <c r="E36">
-        <v>187.608</v>
+        <v>196.77</v>
       </c>
       <c r="F36">
-        <v>311.508</v>
+        <v>320.67</v>
       </c>
       <c r="G36">
         <v>134.4</v>
@@ -4203,37 +4203,37 @@
         <v>0.525</v>
       </c>
       <c r="M36">
-        <v>73.45358639999999</v>
+        <v>75.61398600000001</v>
       </c>
       <c r="N36">
-        <v>-72.92858639999999</v>
+        <v>-75.08898600000001</v>
       </c>
       <c r="O36">
-        <v>-24.795719376</v>
+        <v>-25.53025524</v>
       </c>
       <c r="P36">
-        <v>-48.13286702399999</v>
+        <v>-49.55873076</v>
       </c>
       <c r="Q36">
-        <v>-48.06586702399999</v>
+        <v>-49.49173076</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1303855605043431</v>
+        <v>0.1316868768197945</v>
       </c>
       <c r="T36">
-        <v>1.102433409669732</v>
+        <v>1.119393923664651</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.002430105985948156</v>
+        <v>0.002360674386349636</v>
       </c>
       <c r="W36">
-        <v>0.2352269810085134</v>
+        <v>0.2352433529796988</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.007147370546906395</v>
+        <v>0.006943159959851952</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.167931643475761</v>
+        <v>0.169831643475761</v>
       </c>
       <c r="C37">
-        <v>162.4839234055563</v>
+        <v>147.979476624223</v>
       </c>
       <c r="D37">
-        <v>348.7539234055563</v>
+        <v>343.411476624223</v>
       </c>
       <c r="E37">
-        <v>196.77</v>
+        <v>205.932</v>
       </c>
       <c r="F37">
-        <v>320.67</v>
+        <v>329.832</v>
       </c>
       <c r="G37">
         <v>134.4</v>
@@ -4285,37 +4285,37 @@
         <v>0.525</v>
       </c>
       <c r="M37">
-        <v>75.61398600000001</v>
+        <v>77.7743856</v>
       </c>
       <c r="N37">
-        <v>-75.08898600000001</v>
+        <v>-77.2493856</v>
       </c>
       <c r="O37">
-        <v>-25.53025524</v>
+        <v>-26.264791104</v>
       </c>
       <c r="P37">
-        <v>-49.55873076</v>
+        <v>-50.984594496</v>
       </c>
       <c r="Q37">
-        <v>-49.49173076</v>
+        <v>-50.917594496</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1316868768197945</v>
+        <v>0.1330288592701038</v>
       </c>
       <c r="T37">
-        <v>1.119393923664651</v>
+        <v>1.136884453721911</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.002360674386349636</v>
+        <v>0.002295100097839925</v>
       </c>
       <c r="W37">
-        <v>0.2352433529796988</v>
+        <v>0.2352588153969294</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.006943159959851952</v>
+        <v>0.006750294405411639</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.169831643475761</v>
+        <v>0.171731643475761</v>
       </c>
       <c r="C38">
-        <v>147.979476624223</v>
+        <v>133.6362387115167</v>
       </c>
       <c r="D38">
-        <v>343.4114766242229</v>
+        <v>338.2302387115167</v>
       </c>
       <c r="E38">
-        <v>205.9319999999999</v>
+        <v>215.094</v>
       </c>
       <c r="F38">
-        <v>329.8319999999999</v>
+        <v>338.994</v>
       </c>
       <c r="G38">
         <v>134.4</v>
@@ -4367,37 +4367,37 @@
         <v>0.525</v>
       </c>
       <c r="M38">
-        <v>77.77438559999999</v>
+        <v>79.93478519999999</v>
       </c>
       <c r="N38">
-        <v>-77.24938559999998</v>
+        <v>-79.40978519999999</v>
       </c>
       <c r="O38">
-        <v>-26.264791104</v>
+        <v>-26.999326968</v>
       </c>
       <c r="P38">
-        <v>-50.98459449599999</v>
+        <v>-52.41045823199999</v>
       </c>
       <c r="Q38">
-        <v>-50.91759449599999</v>
+        <v>-52.34345823199999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1330288592701038</v>
+        <v>0.1344134443378832</v>
       </c>
       <c r="T38">
-        <v>1.136884453721911</v>
+        <v>1.154930238701624</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.002295100097839925</v>
+        <v>0.002233070365465873</v>
       </c>
       <c r="W38">
-        <v>0.2352588153969294</v>
+        <v>0.2352734420078232</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.006750294405411639</v>
+        <v>0.00656785401607618</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.171731643475761</v>
+        <v>0.173631643475761</v>
       </c>
       <c r="C39">
-        <v>133.6362387115167</v>
+        <v>119.4470213803577</v>
       </c>
       <c r="D39">
-        <v>338.2302387115167</v>
+        <v>333.2030213803578</v>
       </c>
       <c r="E39">
-        <v>215.094</v>
+        <v>224.256</v>
       </c>
       <c r="F39">
-        <v>338.994</v>
+        <v>348.156</v>
       </c>
       <c r="G39">
         <v>134.4</v>
@@ -4449,37 +4449,37 @@
         <v>0.525</v>
       </c>
       <c r="M39">
-        <v>79.93478519999999</v>
+        <v>82.0951848</v>
       </c>
       <c r="N39">
-        <v>-79.40978519999999</v>
+        <v>-81.57018479999999</v>
       </c>
       <c r="O39">
-        <v>-26.999326968</v>
+        <v>-27.733862832</v>
       </c>
       <c r="P39">
-        <v>-52.41045823199999</v>
+        <v>-53.83632196799999</v>
       </c>
       <c r="Q39">
-        <v>-52.34345823199999</v>
+        <v>-53.76932196799999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1344134443378832</v>
+        <v>0.1358426934401071</v>
       </c>
       <c r="T39">
-        <v>1.154930238701624</v>
+        <v>1.173558145777456</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.002233070365465873</v>
+        <v>0.00217430535584835</v>
       </c>
       <c r="W39">
-        <v>0.2352734420078232</v>
+        <v>0.235287298797091</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.00656785401607618</v>
+        <v>0.006395015752495237</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.173631643475761</v>
+        <v>0.175531643475761</v>
       </c>
       <c r="C40">
-        <v>119.4470213803577</v>
+        <v>105.4050574512723</v>
       </c>
       <c r="D40">
-        <v>333.2030213803578</v>
+        <v>328.3230574512723</v>
       </c>
       <c r="E40">
-        <v>224.256</v>
+        <v>233.418</v>
       </c>
       <c r="F40">
-        <v>348.156</v>
+        <v>357.318</v>
       </c>
       <c r="G40">
         <v>134.4</v>
@@ -4531,37 +4531,37 @@
         <v>0.525</v>
       </c>
       <c r="M40">
-        <v>82.0951848</v>
+        <v>84.2555844</v>
       </c>
       <c r="N40">
-        <v>-81.57018479999999</v>
+        <v>-83.7305844</v>
       </c>
       <c r="O40">
-        <v>-27.733862832</v>
+        <v>-28.468398696</v>
       </c>
       <c r="P40">
-        <v>-53.83632196799999</v>
+        <v>-55.262185704</v>
       </c>
       <c r="Q40">
-        <v>-53.76932196799999</v>
+        <v>-55.195185704</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1358426934401071</v>
+        <v>0.1373188031686335</v>
       </c>
       <c r="T40">
-        <v>1.173558145777456</v>
+        <v>1.192796803904956</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.00217430535584835</v>
+        <v>0.002118553936467623</v>
       </c>
       <c r="W40">
-        <v>0.235287298797091</v>
+        <v>0.2353004449817809</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.006395015752495237</v>
+        <v>0.006231040989610692</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.175531643475761</v>
+        <v>0.177431643475761</v>
       </c>
       <c r="C41">
-        <v>105.4050574512723</v>
+        <v>91.50397046059527</v>
       </c>
       <c r="D41">
-        <v>328.3230574512723</v>
+        <v>323.5839704605953</v>
       </c>
       <c r="E41">
-        <v>233.418</v>
+        <v>242.58</v>
       </c>
       <c r="F41">
-        <v>357.318</v>
+        <v>366.48</v>
       </c>
       <c r="G41">
         <v>134.4</v>
@@ -4613,37 +4613,37 @@
         <v>0.525</v>
       </c>
       <c r="M41">
-        <v>84.2555844</v>
+        <v>86.41598400000001</v>
       </c>
       <c r="N41">
-        <v>-83.7305844</v>
+        <v>-85.890984</v>
       </c>
       <c r="O41">
-        <v>-28.468398696</v>
+        <v>-29.20293456</v>
       </c>
       <c r="P41">
-        <v>-55.262185704</v>
+        <v>-56.68804944</v>
       </c>
       <c r="Q41">
-        <v>-55.195185704</v>
+        <v>-56.62104944</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1373188031686335</v>
+        <v>0.1388441165547774</v>
       </c>
       <c r="T41">
-        <v>1.192796803904956</v>
+        <v>1.212676750636705</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.002118553936467623</v>
+        <v>0.002065590088055932</v>
       </c>
       <c r="W41">
-        <v>0.2353004449817809</v>
+        <v>0.2353129338572364</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.006231040989610692</v>
+        <v>0.00607526496487043</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.177431643475761</v>
+        <v>0.179331643475761</v>
       </c>
       <c r="C42">
-        <v>91.50397046059527</v>
+        <v>77.73774686331188</v>
       </c>
       <c r="D42">
-        <v>323.5839704605953</v>
+        <v>318.9797468633119</v>
       </c>
       <c r="E42">
-        <v>242.58</v>
+        <v>251.742</v>
       </c>
       <c r="F42">
-        <v>366.48</v>
+        <v>375.642</v>
       </c>
       <c r="G42">
         <v>134.4</v>
@@ -4695,37 +4695,37 @@
         <v>0.525</v>
       </c>
       <c r="M42">
-        <v>86.41598400000001</v>
+        <v>88.5763836</v>
       </c>
       <c r="N42">
-        <v>-85.890984</v>
+        <v>-88.05138359999999</v>
       </c>
       <c r="O42">
-        <v>-29.20293456</v>
+        <v>-29.937470424</v>
       </c>
       <c r="P42">
-        <v>-56.68804944</v>
+        <v>-58.113913176</v>
       </c>
       <c r="Q42">
-        <v>-56.62104944</v>
+        <v>-58.046913176</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1388441165547774</v>
+        <v>0.1404211354794346</v>
       </c>
       <c r="T42">
-        <v>1.212676750636705</v>
+        <v>1.233230593867836</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.002065590088055932</v>
+        <v>0.002015209842005788</v>
       </c>
       <c r="W42">
-        <v>0.2353129338572364</v>
+        <v>0.235324813519255</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.00607526496487043</v>
+        <v>0.005927087770605355</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.179331643475761</v>
+        <v>0.181231643475761</v>
       </c>
       <c r="C43">
-        <v>77.73774686331188</v>
+        <v>64.10071057573435</v>
       </c>
       <c r="D43">
-        <v>318.9797468633119</v>
+        <v>314.5047105757344</v>
       </c>
       <c r="E43">
-        <v>251.742</v>
+        <v>260.904</v>
       </c>
       <c r="F43">
-        <v>375.642</v>
+        <v>384.804</v>
       </c>
       <c r="G43">
         <v>134.4</v>
@@ -4777,37 +4777,37 @@
         <v>0.525</v>
       </c>
       <c r="M43">
-        <v>88.5763836</v>
+        <v>90.7367832</v>
       </c>
       <c r="N43">
-        <v>-88.05138359999999</v>
+        <v>-90.2117832</v>
       </c>
       <c r="O43">
-        <v>-29.937470424</v>
+        <v>-30.672006288</v>
       </c>
       <c r="P43">
-        <v>-58.113913176</v>
+        <v>-59.53977691199999</v>
       </c>
       <c r="Q43">
-        <v>-58.046913176</v>
+        <v>-59.47277691199999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1404211354794346</v>
+        <v>0.1420525343670111</v>
       </c>
       <c r="T43">
-        <v>1.233230593867836</v>
+        <v>1.254493190313833</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.002015209842005788</v>
+        <v>0.001967228655291364</v>
       </c>
       <c r="W43">
-        <v>0.235324813519255</v>
+        <v>0.2353361274830823</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.005927087770605355</v>
+        <v>0.00578596663320996</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.181231643475761</v>
+        <v>0.183131643475761</v>
       </c>
       <c r="C44">
-        <v>64.10071057573441</v>
+        <v>50.58749963140923</v>
       </c>
       <c r="D44">
-        <v>314.5047105757344</v>
+        <v>310.1534996314092</v>
       </c>
       <c r="E44">
-        <v>260.904</v>
+        <v>270.0659999999999</v>
       </c>
       <c r="F44">
-        <v>384.804</v>
+        <v>393.966</v>
       </c>
       <c r="G44">
         <v>134.4</v>
@@ -4859,37 +4859,37 @@
         <v>0.525</v>
       </c>
       <c r="M44">
-        <v>90.73678319999999</v>
+        <v>92.8971828</v>
       </c>
       <c r="N44">
-        <v>-90.21178319999999</v>
+        <v>-92.37218279999999</v>
       </c>
       <c r="O44">
-        <v>-30.672006288</v>
+        <v>-31.406542152</v>
       </c>
       <c r="P44">
-        <v>-59.53977691199999</v>
+        <v>-60.96564064799999</v>
       </c>
       <c r="Q44">
-        <v>-59.47277691199999</v>
+        <v>-60.89864064799999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1420525343670111</v>
+        <v>0.1437411753208183</v>
       </c>
       <c r="T44">
-        <v>1.254493190313833</v>
+        <v>1.276501842775479</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.001967228655291364</v>
+        <v>0.001921479151679937</v>
       </c>
       <c r="W44">
-        <v>0.2353361274830823</v>
+        <v>0.2353469152160339</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.00578596663320996</v>
+        <v>0.005651409269646912</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.183131643475761</v>
+        <v>0.185031643475761</v>
       </c>
       <c r="C45">
-        <v>50.58749963140923</v>
+        <v>37.19304474839061</v>
       </c>
       <c r="D45">
-        <v>310.1534996314092</v>
+        <v>305.9210447483906</v>
       </c>
       <c r="E45">
-        <v>270.0659999999999</v>
+        <v>279.228</v>
       </c>
       <c r="F45">
-        <v>393.966</v>
+        <v>403.128</v>
       </c>
       <c r="G45">
         <v>134.4</v>
@@ -4941,37 +4941,37 @@
         <v>0.525</v>
       </c>
       <c r="M45">
-        <v>92.8971828</v>
+        <v>95.0575824</v>
       </c>
       <c r="N45">
-        <v>-92.37218279999999</v>
+        <v>-94.5325824</v>
       </c>
       <c r="O45">
-        <v>-31.406542152</v>
+        <v>-32.141078016</v>
       </c>
       <c r="P45">
-        <v>-60.96564064799999</v>
+        <v>-62.39150438399999</v>
       </c>
       <c r="Q45">
-        <v>-60.89864064799999</v>
+        <v>-62.32450438399999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1437411753208183</v>
+        <v>0.1454901248801186</v>
       </c>
       <c r="T45">
-        <v>1.276501842775479</v>
+        <v>1.299296518539327</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.001921479151679937</v>
+        <v>0.001877809170959938</v>
       </c>
       <c r="W45">
-        <v>0.2353469152160339</v>
+        <v>0.2353572125974877</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.005651409269646912</v>
+        <v>0.005522968149882179</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.185031643475761</v>
+        <v>0.186931643475761</v>
       </c>
       <c r="C46">
-        <v>37.19304474839061</v>
+        <v>23.91254962775702</v>
       </c>
       <c r="D46">
-        <v>305.9210447483906</v>
+        <v>301.8025496277569</v>
       </c>
       <c r="E46">
-        <v>279.228</v>
+        <v>288.39</v>
       </c>
       <c r="F46">
-        <v>403.128</v>
+        <v>412.29</v>
       </c>
       <c r="G46">
         <v>134.4</v>
@@ -5023,37 +5023,37 @@
         <v>0.525</v>
       </c>
       <c r="M46">
-        <v>95.0575824</v>
+        <v>97.21798199999999</v>
       </c>
       <c r="N46">
-        <v>-94.5325824</v>
+        <v>-96.69298199999999</v>
       </c>
       <c r="O46">
-        <v>-32.141078016</v>
+        <v>-32.87561388</v>
       </c>
       <c r="P46">
-        <v>-62.39150438399999</v>
+        <v>-63.81736811999999</v>
       </c>
       <c r="Q46">
-        <v>-62.32450438399999</v>
+        <v>-63.75036811999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1454901248801186</v>
+        <v>0.1473026726052117</v>
       </c>
       <c r="T46">
-        <v>1.299296518539327</v>
+        <v>1.322920091603678</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.001877809170959938</v>
+        <v>0.00183608007827194</v>
       </c>
       <c r="W46">
-        <v>0.2353572125974877</v>
+        <v>0.2353670523175435</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.005522968149882179</v>
+        <v>0.005400235524329333</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.186931643475761</v>
+        <v>0.188831643475761</v>
       </c>
       <c r="C47">
-        <v>23.91254962775702</v>
+        <v>10.74147282238619</v>
       </c>
       <c r="D47">
-        <v>301.8025496277569</v>
+        <v>297.7934728223861</v>
       </c>
       <c r="E47">
-        <v>288.39</v>
+        <v>297.552</v>
       </c>
       <c r="F47">
-        <v>412.29</v>
+        <v>421.452</v>
       </c>
       <c r="G47">
         <v>134.4</v>
@@ -5105,37 +5105,37 @@
         <v>0.525</v>
       </c>
       <c r="M47">
-        <v>97.21798199999999</v>
+        <v>99.3783816</v>
       </c>
       <c r="N47">
-        <v>-96.69298199999999</v>
+        <v>-98.85338159999999</v>
       </c>
       <c r="O47">
-        <v>-32.87561388</v>
+        <v>-33.610149744</v>
       </c>
       <c r="P47">
-        <v>-63.81736811999999</v>
+        <v>-65.24323185599999</v>
       </c>
       <c r="Q47">
-        <v>-63.75036811999999</v>
+        <v>-65.176231856</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1473026726052117</v>
+        <v>0.1491823517275304</v>
       </c>
       <c r="T47">
-        <v>1.322920091603678</v>
+        <v>1.347418611818561</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.00183608007827194</v>
+        <v>0.00179616529396168</v>
       </c>
       <c r="W47">
-        <v>0.2353670523175435</v>
+        <v>0.2353764642236839</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.005400235524329333</v>
+        <v>0.00528283909988736</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.188831643475761</v>
+        <v>0.190731643475761</v>
       </c>
       <c r="C48">
-        <v>10.74147282238619</v>
+        <v>-2.324488968105527</v>
       </c>
       <c r="D48">
-        <v>297.7934728223861</v>
+        <v>293.8895110318945</v>
       </c>
       <c r="E48">
-        <v>297.552</v>
+        <v>306.7139999999999</v>
       </c>
       <c r="F48">
-        <v>421.452</v>
+        <v>430.614</v>
       </c>
       <c r="G48">
         <v>134.4</v>
@@ -5187,37 +5187,37 @@
         <v>0.525</v>
       </c>
       <c r="M48">
-        <v>99.3783816</v>
+        <v>101.5387812</v>
       </c>
       <c r="N48">
-        <v>-98.85338159999999</v>
+        <v>-101.0137812</v>
       </c>
       <c r="O48">
-        <v>-33.610149744</v>
+        <v>-34.344685608</v>
       </c>
       <c r="P48">
-        <v>-65.24323185599999</v>
+        <v>-66.66909559199999</v>
       </c>
       <c r="Q48">
-        <v>-65.176231856</v>
+        <v>-66.602095592</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1491823517275304</v>
+        <v>0.1511329621374838</v>
       </c>
       <c r="T48">
-        <v>1.347418611818561</v>
+        <v>1.372841604494383</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.00179616529396168</v>
+        <v>0.001757949011111431</v>
       </c>
       <c r="W48">
-        <v>0.2353764642236839</v>
+        <v>0.2353854756231799</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.00528283909988736</v>
+        <v>0.005170438267974808</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.190731643475761</v>
+        <v>0.192631643475761</v>
       </c>
       <c r="C49">
-        <v>-2.324488968105527</v>
+        <v>-15.28941630544608</v>
       </c>
       <c r="D49">
-        <v>293.8895110318945</v>
+        <v>290.086583694554</v>
       </c>
       <c r="E49">
-        <v>306.7139999999999</v>
+        <v>315.876</v>
       </c>
       <c r="F49">
-        <v>430.614</v>
+        <v>439.776</v>
       </c>
       <c r="G49">
         <v>134.4</v>
@@ -5269,37 +5269,37 @@
         <v>0.525</v>
       </c>
       <c r="M49">
-        <v>101.5387812</v>
+        <v>103.6991808</v>
       </c>
       <c r="N49">
-        <v>-101.0137812</v>
+        <v>-103.1741808</v>
       </c>
       <c r="O49">
-        <v>-34.344685608</v>
+        <v>-35.079221472</v>
       </c>
       <c r="P49">
-        <v>-66.66909559199999</v>
+        <v>-68.094959328</v>
       </c>
       <c r="Q49">
-        <v>-66.602095592</v>
+        <v>-68.02795932800001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1511329621374838</v>
+        <v>0.1531585960247431</v>
       </c>
       <c r="T49">
-        <v>1.372841604494383</v>
+        <v>1.399242404580813</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.001757949011111431</v>
+        <v>0.001721325073379943</v>
       </c>
       <c r="W49">
-        <v>0.2353854756231799</v>
+        <v>0.235394111547697</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.005170438267974808</v>
+        <v>0.005062720804058674</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.192631643475761</v>
+        <v>0.194531643475761</v>
       </c>
       <c r="C50">
-        <v>-15.28941630544603</v>
+        <v>-28.15718123978871</v>
       </c>
       <c r="D50">
-        <v>290.086583694554</v>
+        <v>286.3808187602112</v>
       </c>
       <c r="E50">
-        <v>315.876</v>
+        <v>325.0379999999999</v>
       </c>
       <c r="F50">
-        <v>439.776</v>
+        <v>448.9379999999999</v>
       </c>
       <c r="G50">
         <v>134.4</v>
@@ -5351,37 +5351,37 @@
         <v>0.525</v>
       </c>
       <c r="M50">
-        <v>103.6991808</v>
+        <v>105.8595804</v>
       </c>
       <c r="N50">
-        <v>-103.1741808</v>
+        <v>-105.3345804</v>
       </c>
       <c r="O50">
-        <v>-35.079221472</v>
+        <v>-35.81375733599999</v>
       </c>
       <c r="P50">
-        <v>-68.09495932799999</v>
+        <v>-69.52082306399998</v>
       </c>
       <c r="Q50">
-        <v>-68.02795932799999</v>
+        <v>-69.45382306399999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1531585960247431</v>
+        <v>0.1552636665350322</v>
       </c>
       <c r="T50">
-        <v>1.399242404580813</v>
+        <v>1.426678530160829</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.001721325073379944</v>
+        <v>0.001686195990249741</v>
       </c>
       <c r="W50">
-        <v>0.235394111547697</v>
+        <v>0.2354023949854991</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.005062720804058674</v>
+        <v>0.004959399971322775</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.194531643475761</v>
+        <v>0.196431643475761</v>
       </c>
       <c r="C51">
-        <v>-28.15718123978871</v>
+        <v>-40.93146046007058</v>
       </c>
       <c r="D51">
-        <v>286.3808187602112</v>
+        <v>282.7685395399293</v>
       </c>
       <c r="E51">
-        <v>325.0379999999999</v>
+        <v>334.1999999999999</v>
       </c>
       <c r="F51">
-        <v>448.9379999999999</v>
+        <v>458.1</v>
       </c>
       <c r="G51">
         <v>134.4</v>
@@ -5433,37 +5433,37 @@
         <v>0.525</v>
       </c>
       <c r="M51">
-        <v>105.8595804</v>
+        <v>108.01998</v>
       </c>
       <c r="N51">
-        <v>-105.3345804</v>
+        <v>-107.49498</v>
       </c>
       <c r="O51">
-        <v>-35.81375733599999</v>
+        <v>-36.5482932</v>
       </c>
       <c r="P51">
-        <v>-69.52082306399998</v>
+        <v>-70.94668679999998</v>
       </c>
       <c r="Q51">
-        <v>-69.45382306399999</v>
+        <v>-70.87968679999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1552636665350322</v>
+        <v>0.1574529398657329</v>
       </c>
       <c r="T51">
-        <v>1.426678530160829</v>
+        <v>1.455212100764046</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.001686195990249741</v>
+        <v>0.001652472070444746</v>
       </c>
       <c r="W51">
-        <v>0.2354023949854991</v>
+        <v>0.2354103470857891</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.004959399971322775</v>
+        <v>0.004860211971896344</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.196431643475761</v>
+        <v>0.198331643475761</v>
       </c>
       <c r="C52">
-        <v>-40.93146046007058</v>
+        <v>-53.61574746152979</v>
       </c>
       <c r="D52">
-        <v>282.7685395399293</v>
+        <v>279.2462525384702</v>
       </c>
       <c r="E52">
-        <v>334.1999999999999</v>
+        <v>343.362</v>
       </c>
       <c r="F52">
-        <v>458.1</v>
+        <v>467.262</v>
       </c>
       <c r="G52">
         <v>134.4</v>
@@ -5515,37 +5515,37 @@
         <v>0.525</v>
       </c>
       <c r="M52">
-        <v>108.01998</v>
+        <v>110.1803796</v>
       </c>
       <c r="N52">
-        <v>-107.49498</v>
+        <v>-109.6553796</v>
       </c>
       <c r="O52">
-        <v>-36.5482932</v>
+        <v>-37.282829064</v>
       </c>
       <c r="P52">
-        <v>-70.94668679999998</v>
+        <v>-72.37255053600001</v>
       </c>
       <c r="Q52">
-        <v>-70.87968679999999</v>
+        <v>-72.30555053600001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1574529398657329</v>
+        <v>0.1597315712915642</v>
       </c>
       <c r="T52">
-        <v>1.455212100764046</v>
+        <v>1.484910306902088</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.001652472070444746</v>
+        <v>0.00162007065729877</v>
       </c>
       <c r="W52">
-        <v>0.2354103470857891</v>
+        <v>0.235417987339009</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.004860211971896344</v>
+        <v>0.004764913697937634</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.198331643475761</v>
+        <v>0.200231643475761</v>
       </c>
       <c r="C53">
-        <v>-53.61574746152979</v>
+        <v>-66.21336381502897</v>
       </c>
       <c r="D53">
-        <v>279.2462525384702</v>
+        <v>275.810636184971</v>
       </c>
       <c r="E53">
-        <v>343.362</v>
+        <v>352.524</v>
       </c>
       <c r="F53">
-        <v>467.262</v>
+        <v>476.424</v>
       </c>
       <c r="G53">
         <v>134.4</v>
@@ -5597,37 +5597,37 @@
         <v>0.525</v>
       </c>
       <c r="M53">
-        <v>110.1803796</v>
+        <v>112.3407792</v>
       </c>
       <c r="N53">
-        <v>-109.6553796</v>
+        <v>-111.8157792</v>
       </c>
       <c r="O53">
-        <v>-37.282829064</v>
+        <v>-38.017364928</v>
       </c>
       <c r="P53">
-        <v>-72.37255053600001</v>
+        <v>-73.798414272</v>
       </c>
       <c r="Q53">
-        <v>-72.30555053600001</v>
+        <v>-73.73141427200001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1597315712915642</v>
+        <v>0.1621051456934717</v>
       </c>
       <c r="T53">
-        <v>1.484910306902088</v>
+        <v>1.515845938295881</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.00162007065729877</v>
+        <v>0.001588915452350717</v>
       </c>
       <c r="W53">
-        <v>0.235417987339009</v>
+        <v>0.2354253337363357</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.004764913697937634</v>
+        <v>0.004673280742208075</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.200231643475761</v>
+        <v>0.202131643475761</v>
       </c>
       <c r="C54">
-        <v>-66.21336381502897</v>
+        <v>-78.72746961459939</v>
       </c>
       <c r="D54">
-        <v>275.810636184971</v>
+        <v>272.4585303854006</v>
       </c>
       <c r="E54">
-        <v>352.524</v>
+        <v>361.686</v>
       </c>
       <c r="F54">
-        <v>476.424</v>
+        <v>485.586</v>
       </c>
       <c r="G54">
         <v>134.4</v>
@@ -5679,37 +5679,37 @@
         <v>0.525</v>
       </c>
       <c r="M54">
-        <v>112.3407792</v>
+        <v>114.5011788</v>
       </c>
       <c r="N54">
-        <v>-111.8157792</v>
+        <v>-113.9761788</v>
       </c>
       <c r="O54">
-        <v>-38.017364928</v>
+        <v>-38.751900792</v>
       </c>
       <c r="P54">
-        <v>-73.798414272</v>
+        <v>-75.224278008</v>
       </c>
       <c r="Q54">
-        <v>-73.73141427200001</v>
+        <v>-75.15727800800001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1621051456934717</v>
+        <v>0.164579723261418</v>
       </c>
       <c r="T54">
-        <v>1.515845938295881</v>
+        <v>1.548097979536219</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.001588915452350717</v>
+        <v>0.001558935915513911</v>
       </c>
       <c r="W54">
-        <v>0.2354253337363357</v>
+        <v>0.2354324029111218</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.004673280742208075</v>
+        <v>0.004585105633864495</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.202131643475761</v>
+        <v>0.204031643475761</v>
       </c>
       <c r="C55">
-        <v>-78.72746961459939</v>
+        <v>-91.16107317227562</v>
       </c>
       <c r="D55">
-        <v>272.4585303854006</v>
+        <v>269.1869268277244</v>
       </c>
       <c r="E55">
-        <v>361.686</v>
+        <v>370.848</v>
       </c>
       <c r="F55">
-        <v>485.586</v>
+        <v>494.748</v>
       </c>
       <c r="G55">
         <v>134.4</v>
@@ -5761,37 +5761,37 @@
         <v>0.525</v>
       </c>
       <c r="M55">
-        <v>114.5011788</v>
+        <v>116.6615784</v>
       </c>
       <c r="N55">
-        <v>-113.9761788</v>
+        <v>-116.1365784</v>
       </c>
       <c r="O55">
-        <v>-38.751900792</v>
+        <v>-39.486436656</v>
       </c>
       <c r="P55">
-        <v>-75.224278008</v>
+        <v>-76.650141744</v>
       </c>
       <c r="Q55">
-        <v>-75.15727800800001</v>
+        <v>-76.583141744</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.164579723261418</v>
+        <v>0.1671618911584053</v>
       </c>
       <c r="T55">
-        <v>1.548097979536219</v>
+        <v>1.581752283439181</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.001558935915513911</v>
+        <v>0.001530066731893283</v>
       </c>
       <c r="W55">
-        <v>0.2354324029111218</v>
+        <v>0.2354392102646196</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.004585105633864495</v>
+        <v>0.004500196270274426</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.204031643475761</v>
+        <v>0.205931643475761</v>
       </c>
       <c r="C56">
-        <v>-91.16107317227562</v>
+        <v>-103.5170400227444</v>
       </c>
       <c r="D56">
-        <v>269.1869268277244</v>
+        <v>265.9929599772556</v>
       </c>
       <c r="E56">
-        <v>370.848</v>
+        <v>380.01</v>
       </c>
       <c r="F56">
-        <v>494.748</v>
+        <v>503.91</v>
       </c>
       <c r="G56">
         <v>134.4</v>
@@ -5843,37 +5843,37 @@
         <v>0.525</v>
       </c>
       <c r="M56">
-        <v>116.6615784</v>
+        <v>118.821978</v>
       </c>
       <c r="N56">
-        <v>-116.1365784</v>
+        <v>-118.296978</v>
       </c>
       <c r="O56">
-        <v>-39.486436656</v>
+        <v>-40.22097252</v>
       </c>
       <c r="P56">
-        <v>-76.650141744</v>
+        <v>-78.07600548000001</v>
       </c>
       <c r="Q56">
-        <v>-76.583141744</v>
+        <v>-78.00900548000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1671618911584053</v>
+        <v>0.1698588220730365</v>
       </c>
       <c r="T56">
-        <v>1.581752283439181</v>
+        <v>1.616902334182273</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.001530066731893283</v>
+        <v>0.001502247336767951</v>
       </c>
       <c r="W56">
-        <v>0.2354392102646196</v>
+        <v>0.2354457700779901</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.004500196270274426</v>
+        <v>0.004418374519905788</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.205931643475761</v>
+        <v>0.207831643475761</v>
       </c>
       <c r="C57">
-        <v>-103.5170400227444</v>
+        <v>-115.7981012944546</v>
       </c>
       <c r="D57">
-        <v>265.9929599772556</v>
+        <v>262.8738987055455</v>
       </c>
       <c r="E57">
-        <v>380.01</v>
+        <v>389.172</v>
       </c>
       <c r="F57">
-        <v>503.91</v>
+        <v>513.072</v>
       </c>
       <c r="G57">
         <v>134.4</v>
@@ -5925,37 +5925,37 @@
         <v>0.525</v>
       </c>
       <c r="M57">
-        <v>118.821978</v>
+        <v>120.9823776</v>
       </c>
       <c r="N57">
-        <v>-118.296978</v>
+        <v>-120.4573776</v>
       </c>
       <c r="O57">
-        <v>-40.22097252</v>
+        <v>-40.95550838400001</v>
       </c>
       <c r="P57">
-        <v>-78.07600548000001</v>
+        <v>-79.50186921599999</v>
       </c>
       <c r="Q57">
-        <v>-78.00900548000001</v>
+        <v>-79.434869216</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1698588220730365</v>
+        <v>0.1726783407565146</v>
       </c>
       <c r="T57">
-        <v>1.616902334182273</v>
+        <v>1.653650114504598</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.001502247336767951</v>
+        <v>0.001475421491468523</v>
       </c>
       <c r="W57">
-        <v>0.2354457700779901</v>
+        <v>0.2354520956123117</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.004418374519905788</v>
+        <v>0.004339474974907498</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.207831643475761</v>
+        <v>0.209731643475761</v>
       </c>
       <c r="C58">
-        <v>-115.7981012944546</v>
+        <v>-128.0068614985904</v>
       </c>
       <c r="D58">
-        <v>262.8738987055455</v>
+        <v>259.8271385014096</v>
       </c>
       <c r="E58">
-        <v>389.172</v>
+        <v>398.3340000000001</v>
       </c>
       <c r="F58">
-        <v>513.072</v>
+        <v>522.234</v>
       </c>
       <c r="G58">
         <v>134.4</v>
@@ -6007,37 +6007,37 @@
         <v>0.525</v>
       </c>
       <c r="M58">
-        <v>120.9823776</v>
+        <v>123.1427772</v>
       </c>
       <c r="N58">
-        <v>-120.4573776</v>
+        <v>-122.6177772</v>
       </c>
       <c r="O58">
-        <v>-40.95550838400001</v>
+        <v>-41.69004424800001</v>
       </c>
       <c r="P58">
-        <v>-79.50186921599999</v>
+        <v>-80.927732952</v>
       </c>
       <c r="Q58">
-        <v>-79.434869216</v>
+        <v>-80.86073295200001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1726783407565146</v>
+        <v>0.1756289998438754</v>
       </c>
       <c r="T58">
-        <v>1.653650114504598</v>
+        <v>1.692107093911681</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.001475421491468523</v>
+        <v>0.001449536903898899</v>
       </c>
       <c r="W58">
-        <v>0.2354520956123117</v>
+        <v>0.2354581991980606</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.004339474974907498</v>
+        <v>0.004263343834996824</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.209731643475761</v>
+        <v>0.211631643475761</v>
       </c>
       <c r="C59">
-        <v>-128.0068614985904</v>
+        <v>-140.1458057825976</v>
       </c>
       <c r="D59">
-        <v>259.8271385014096</v>
+        <v>256.8501942174025</v>
       </c>
       <c r="E59">
-        <v>398.3340000000001</v>
+        <v>407.4960000000001</v>
       </c>
       <c r="F59">
-        <v>522.234</v>
+        <v>531.3960000000001</v>
       </c>
       <c r="G59">
         <v>134.4</v>
@@ -6089,37 +6089,37 @@
         <v>0.525</v>
       </c>
       <c r="M59">
-        <v>123.1427772</v>
+        <v>125.3031768</v>
       </c>
       <c r="N59">
-        <v>-122.6177772</v>
+        <v>-124.7781768</v>
       </c>
       <c r="O59">
-        <v>-41.69004424800001</v>
+        <v>-42.42458011200001</v>
       </c>
       <c r="P59">
-        <v>-80.927732952</v>
+        <v>-82.35359668800001</v>
       </c>
       <c r="Q59">
-        <v>-80.86073295200001</v>
+        <v>-82.28659668800002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1756289998438754</v>
+        <v>0.1787201665068248</v>
       </c>
       <c r="T59">
-        <v>1.692107093911681</v>
+        <v>1.732395358052436</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.001449536903898899</v>
+        <v>0.001424544888314436</v>
       </c>
       <c r="W59">
-        <v>0.2354581991980606</v>
+        <v>0.2354640923153355</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.004263343834996824</v>
+        <v>0.004189837906807159</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.211631643475761</v>
+        <v>0.213531643475761</v>
       </c>
       <c r="C60">
-        <v>-140.1458057825974</v>
+        <v>-152.2173066907167</v>
       </c>
       <c r="D60">
-        <v>256.8501942174025</v>
+        <v>253.9406933092832</v>
       </c>
       <c r="E60">
-        <v>407.496</v>
+        <v>416.6579999999999</v>
       </c>
       <c r="F60">
-        <v>531.396</v>
+        <v>540.5579999999999</v>
       </c>
       <c r="G60">
         <v>134.4</v>
@@ -6171,37 +6171,37 @@
         <v>0.525</v>
       </c>
       <c r="M60">
-        <v>125.3031768</v>
+        <v>127.4635764</v>
       </c>
       <c r="N60">
-        <v>-124.7781768</v>
+        <v>-126.9385764</v>
       </c>
       <c r="O60">
-        <v>-42.42458011199999</v>
+        <v>-43.159115976</v>
       </c>
       <c r="P60">
-        <v>-82.35359668799998</v>
+        <v>-83.77946042399998</v>
       </c>
       <c r="Q60">
-        <v>-82.28659668799999</v>
+        <v>-83.71246042399999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1787201665068248</v>
+        <v>0.1819621217874791</v>
       </c>
       <c r="T60">
-        <v>1.732395358052435</v>
+        <v>1.774648903370788</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.001424544888314436</v>
+        <v>0.001400400059698937</v>
       </c>
       <c r="W60">
-        <v>0.2354640923153355</v>
+        <v>0.235469785665923</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.004189837906807159</v>
+        <v>0.004118823704996943</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.213531643475761</v>
+        <v>0.215431643475761</v>
       </c>
       <c r="C61">
-        <v>-152.2173066907167</v>
+        <v>-164.2236304701805</v>
       </c>
       <c r="D61">
-        <v>253.9406933092832</v>
+        <v>251.0963695298194</v>
       </c>
       <c r="E61">
-        <v>416.6579999999999</v>
+        <v>425.8199999999999</v>
       </c>
       <c r="F61">
-        <v>540.5579999999999</v>
+        <v>549.7199999999999</v>
       </c>
       <c r="G61">
         <v>134.4</v>
@@ -6253,37 +6253,37 @@
         <v>0.525</v>
       </c>
       <c r="M61">
-        <v>127.4635764</v>
+        <v>129.623976</v>
       </c>
       <c r="N61">
-        <v>-126.9385764</v>
+        <v>-129.098976</v>
       </c>
       <c r="O61">
-        <v>-43.159115976</v>
+        <v>-43.89365184</v>
       </c>
       <c r="P61">
-        <v>-83.77946042399998</v>
+        <v>-85.20532415999999</v>
       </c>
       <c r="Q61">
-        <v>-83.71246042399999</v>
+        <v>-85.13832416</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1819621217874791</v>
+        <v>0.1853661748321661</v>
       </c>
       <c r="T61">
-        <v>1.774648903370788</v>
+        <v>1.819015125955057</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.001400400059698937</v>
+        <v>0.001377060058703955</v>
       </c>
       <c r="W61">
-        <v>0.235469785665923</v>
+        <v>0.2354752892381576</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.004118823704996943</v>
+        <v>0.004050176643246917</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.215431643475761</v>
+        <v>0.217331643475761</v>
       </c>
       <c r="C62">
-        <v>-164.2236304701805</v>
+        <v>-176.1669429582993</v>
       </c>
       <c r="D62">
-        <v>251.0963695298194</v>
+        <v>248.3150570417007</v>
       </c>
       <c r="E62">
-        <v>425.8199999999999</v>
+        <v>434.982</v>
       </c>
       <c r="F62">
-        <v>549.7199999999999</v>
+        <v>558.8819999999999</v>
       </c>
       <c r="G62">
         <v>134.4</v>
@@ -6335,37 +6335,37 @@
         <v>0.525</v>
       </c>
       <c r="M62">
-        <v>129.623976</v>
+        <v>131.7843756</v>
       </c>
       <c r="N62">
-        <v>-129.098976</v>
+        <v>-131.2593756</v>
       </c>
       <c r="O62">
-        <v>-43.89365184</v>
+        <v>-44.62818770400001</v>
       </c>
       <c r="P62">
-        <v>-85.20532415999999</v>
+        <v>-86.631187896</v>
       </c>
       <c r="Q62">
-        <v>-85.13832416</v>
+        <v>-86.56418789600001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1853661748321661</v>
+        <v>0.1889447946996575</v>
       </c>
       <c r="T62">
-        <v>1.819015125955057</v>
+        <v>1.865656539441084</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.001377060058703955</v>
+        <v>0.001354485303643234</v>
       </c>
       <c r="W62">
-        <v>0.2354752892381576</v>
+        <v>0.2354806123654009</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.004050176643246917</v>
+        <v>0.00398378030483304</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.217331643475761</v>
+        <v>0.219231643475761</v>
       </c>
       <c r="C63">
-        <v>-176.1669429582993</v>
+        <v>-188.0493150825776</v>
       </c>
       <c r="D63">
-        <v>248.3150570417007</v>
+        <v>245.5946849174224</v>
       </c>
       <c r="E63">
-        <v>434.982</v>
+        <v>444.144</v>
       </c>
       <c r="F63">
-        <v>558.8819999999999</v>
+        <v>568.044</v>
       </c>
       <c r="G63">
         <v>134.4</v>
@@ -6417,37 +6417,37 @@
         <v>0.525</v>
       </c>
       <c r="M63">
-        <v>131.7843756</v>
+        <v>133.9447752</v>
       </c>
       <c r="N63">
-        <v>-131.2593756</v>
+        <v>-133.4197752</v>
       </c>
       <c r="O63">
-        <v>-44.62818770400001</v>
+        <v>-45.36272356800001</v>
       </c>
       <c r="P63">
-        <v>-86.631187896</v>
+        <v>-88.057051632</v>
       </c>
       <c r="Q63">
-        <v>-86.56418789600001</v>
+        <v>-87.990051632</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1889447946996575</v>
+        <v>0.1927117629812274</v>
       </c>
       <c r="T63">
-        <v>1.865656539441084</v>
+        <v>1.914752764163218</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.001354485303643234</v>
+        <v>0.001332638766487698</v>
       </c>
       <c r="W63">
-        <v>0.2354806123654009</v>
+        <v>0.2354857637788622</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.00398378030483304</v>
+        <v>0.003919525783787403</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.219231643475761</v>
+        <v>0.221131643475761</v>
       </c>
       <c r="C64">
-        <v>-188.0493150825776</v>
+        <v>-199.8727280032157</v>
       </c>
       <c r="D64">
-        <v>245.5946849174224</v>
+        <v>242.9332719967843</v>
       </c>
       <c r="E64">
-        <v>444.144</v>
+        <v>453.306</v>
       </c>
       <c r="F64">
-        <v>568.044</v>
+        <v>577.206</v>
       </c>
       <c r="G64">
         <v>134.4</v>
@@ -6499,37 +6499,37 @@
         <v>0.525</v>
       </c>
       <c r="M64">
-        <v>133.9447752</v>
+        <v>136.1051748</v>
       </c>
       <c r="N64">
-        <v>-133.4197752</v>
+        <v>-135.5801748</v>
       </c>
       <c r="O64">
-        <v>-45.36272356800001</v>
+        <v>-46.09725943200001</v>
       </c>
       <c r="P64">
-        <v>-88.057051632</v>
+        <v>-89.48291536799999</v>
       </c>
       <c r="Q64">
-        <v>-87.990051632</v>
+        <v>-89.415915368</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1927117629812274</v>
+        <v>0.1966823511699093</v>
       </c>
       <c r="T64">
-        <v>1.914752764163218</v>
+        <v>1.966502838870332</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.001332638766487698</v>
+        <v>0.001311485770194242</v>
       </c>
       <c r="W64">
-        <v>0.2354857637788622</v>
+        <v>0.2354907516553882</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.003919525783787403</v>
+        <v>0.003857311088806603</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.221131643475761</v>
+        <v>0.223031643475761</v>
       </c>
       <c r="C65">
-        <v>-199.8727280032157</v>
+        <v>-211.6390779248312</v>
       </c>
       <c r="D65">
-        <v>242.9332719967843</v>
+        <v>240.3289220751687</v>
       </c>
       <c r="E65">
-        <v>453.306</v>
+        <v>462.468</v>
       </c>
       <c r="F65">
-        <v>577.206</v>
+        <v>586.3679999999999</v>
       </c>
       <c r="G65">
         <v>134.4</v>
@@ -6581,37 +6581,37 @@
         <v>0.525</v>
       </c>
       <c r="M65">
-        <v>136.1051748</v>
+        <v>138.2655744</v>
       </c>
       <c r="N65">
-        <v>-135.5801748</v>
+        <v>-137.7405744</v>
       </c>
       <c r="O65">
-        <v>-46.09725943200001</v>
+        <v>-46.831795296</v>
       </c>
       <c r="P65">
-        <v>-89.48291536799999</v>
+        <v>-90.90877910399999</v>
       </c>
       <c r="Q65">
-        <v>-89.415915368</v>
+        <v>-90.841779104</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1966823511699093</v>
+        <v>0.2008735275912957</v>
       </c>
       <c r="T65">
-        <v>1.966502838870332</v>
+        <v>2.021127917727842</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.001311485770194242</v>
+        <v>0.001290993805034958</v>
       </c>
       <c r="W65">
-        <v>0.2354907516553882</v>
+        <v>0.2354955836607728</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.003857311088806603</v>
+        <v>0.003797040603044088</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.223031643475761</v>
+        <v>0.224931643475761</v>
       </c>
       <c r="C66">
-        <v>-211.6390779248312</v>
+        <v>-223.3501806019616</v>
       </c>
       <c r="D66">
-        <v>240.3289220751687</v>
+        <v>237.7798193980384</v>
       </c>
       <c r="E66">
-        <v>462.468</v>
+        <v>471.63</v>
       </c>
       <c r="F66">
-        <v>586.3679999999999</v>
+        <v>595.53</v>
       </c>
       <c r="G66">
         <v>134.4</v>
@@ -6663,37 +6663,37 @@
         <v>0.525</v>
       </c>
       <c r="M66">
-        <v>138.2655744</v>
+        <v>140.425974</v>
       </c>
       <c r="N66">
-        <v>-137.7405744</v>
+        <v>-139.900974</v>
       </c>
       <c r="O66">
-        <v>-46.831795296</v>
+        <v>-47.56633116</v>
       </c>
       <c r="P66">
-        <v>-90.90877910399999</v>
+        <v>-92.33464283999999</v>
       </c>
       <c r="Q66">
-        <v>-90.841779104</v>
+        <v>-92.26764283999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2008735275912957</v>
+        <v>0.2053041998081898</v>
       </c>
       <c r="T66">
-        <v>2.021127917727842</v>
+        <v>2.078874429662923</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.001290993805034958</v>
+        <v>0.001271132361880574</v>
       </c>
       <c r="W66">
-        <v>0.2354955836607728</v>
+        <v>0.2355002669890686</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.003797040603044088</v>
+        <v>0.003738624593766393</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.224931643475761</v>
+        <v>0.226831643475761</v>
       </c>
       <c r="C67">
-        <v>-223.3501806019616</v>
+        <v>-235.0077755608438</v>
       </c>
       <c r="D67">
-        <v>237.7798193980384</v>
+        <v>235.2842244391562</v>
       </c>
       <c r="E67">
-        <v>471.63</v>
+        <v>480.792</v>
       </c>
       <c r="F67">
-        <v>595.53</v>
+        <v>604.692</v>
       </c>
       <c r="G67">
         <v>134.4</v>
@@ -6745,37 +6745,37 @@
         <v>0.525</v>
       </c>
       <c r="M67">
-        <v>140.425974</v>
+        <v>142.5863736</v>
       </c>
       <c r="N67">
-        <v>-139.900974</v>
+        <v>-142.0613736</v>
       </c>
       <c r="O67">
-        <v>-47.56633116</v>
+        <v>-48.300867024</v>
       </c>
       <c r="P67">
-        <v>-92.33464283999999</v>
+        <v>-93.760506576</v>
       </c>
       <c r="Q67">
-        <v>-92.26764283999999</v>
+        <v>-93.693506576</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2053041998081898</v>
+        <v>0.2099954998025483</v>
       </c>
       <c r="T67">
-        <v>2.078874429662923</v>
+        <v>2.140017795241244</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.001271132361880574</v>
+        <v>0.001251872780639959</v>
       </c>
       <c r="W67">
-        <v>0.2355002669890686</v>
+        <v>0.2355048083983251</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.003738624593766393</v>
+        <v>0.003681978766588156</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.226831643475761</v>
+        <v>0.228731643475761</v>
       </c>
       <c r="C68">
-        <v>-235.0077755608438</v>
+        <v>-246.6135300581002</v>
       </c>
       <c r="D68">
-        <v>235.2842244391562</v>
+        <v>232.8404699418998</v>
       </c>
       <c r="E68">
-        <v>480.792</v>
+        <v>489.9540000000001</v>
       </c>
       <c r="F68">
-        <v>604.692</v>
+        <v>613.854</v>
       </c>
       <c r="G68">
         <v>134.4</v>
@@ -6827,37 +6827,37 @@
         <v>0.525</v>
       </c>
       <c r="M68">
-        <v>142.5863736</v>
+        <v>144.7467732</v>
       </c>
       <c r="N68">
-        <v>-142.0613736</v>
+        <v>-144.2217732</v>
       </c>
       <c r="O68">
-        <v>-48.300867024</v>
+        <v>-49.03540288800001</v>
       </c>
       <c r="P68">
-        <v>-93.760506576</v>
+        <v>-95.18637031199999</v>
       </c>
       <c r="Q68">
-        <v>-93.693506576</v>
+        <v>-95.119370312</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2099954998025483</v>
+        <v>0.2149711210086862</v>
       </c>
       <c r="T68">
-        <v>2.140017795241244</v>
+        <v>2.204866819339464</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.001251872780639959</v>
+        <v>0.001233188112272198</v>
       </c>
       <c r="W68">
-        <v>0.2355048083983251</v>
+        <v>0.2355092142431262</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.003681978766588156</v>
+        <v>0.003627023859624101</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.228731643475761</v>
+        <v>0.230631643475761</v>
       </c>
       <c r="C69">
-        <v>-246.6135300581002</v>
+        <v>-258.169042795261</v>
       </c>
       <c r="D69">
-        <v>232.8404699418998</v>
+        <v>230.4469572047389</v>
       </c>
       <c r="E69">
-        <v>489.9540000000001</v>
+        <v>499.116</v>
       </c>
       <c r="F69">
-        <v>613.854</v>
+        <v>623.016</v>
       </c>
       <c r="G69">
         <v>134.4</v>
@@ -6909,37 +6909,37 @@
         <v>0.525</v>
       </c>
       <c r="M69">
-        <v>144.7467732</v>
+        <v>146.9071728</v>
       </c>
       <c r="N69">
-        <v>-144.2217732</v>
+        <v>-146.3821728</v>
       </c>
       <c r="O69">
-        <v>-49.03540288800001</v>
+        <v>-49.76993875199999</v>
       </c>
       <c r="P69">
-        <v>-95.18637031199999</v>
+        <v>-96.61223404799998</v>
       </c>
       <c r="Q69">
-        <v>-95.119370312</v>
+        <v>-96.54523404799998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2149711210086862</v>
+        <v>0.2202577185402076</v>
       </c>
       <c r="T69">
-        <v>2.204866819339464</v>
+        <v>2.273768907443822</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.001233188112272198</v>
+        <v>0.001215052992974078</v>
       </c>
       <c r="W69">
-        <v>0.2355092142431262</v>
+        <v>0.2355134905042567</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.003627023859624101</v>
+        <v>0.003573685273453253</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.230631643475761</v>
+        <v>0.232531643475761</v>
       </c>
       <c r="C70">
-        <v>-258.169042795261</v>
+        <v>-269.6758474065151</v>
       </c>
       <c r="D70">
-        <v>230.4469572047389</v>
+        <v>228.1021525934849</v>
       </c>
       <c r="E70">
-        <v>499.116</v>
+        <v>508.278</v>
       </c>
       <c r="F70">
-        <v>623.016</v>
+        <v>632.178</v>
       </c>
       <c r="G70">
         <v>134.4</v>
@@ -6991,37 +6991,37 @@
         <v>0.525</v>
       </c>
       <c r="M70">
-        <v>146.9071728</v>
+        <v>149.0675724</v>
       </c>
       <c r="N70">
-        <v>-146.3821728</v>
+        <v>-148.5425724</v>
       </c>
       <c r="O70">
-        <v>-49.76993875199999</v>
+        <v>-50.50447461600001</v>
       </c>
       <c r="P70">
-        <v>-96.61223404799998</v>
+        <v>-98.038097784</v>
       </c>
       <c r="Q70">
-        <v>-96.54523404799998</v>
+        <v>-97.97109778400001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2202577185402076</v>
+        <v>0.2258853868802143</v>
       </c>
       <c r="T70">
-        <v>2.273768907443822</v>
+        <v>2.347116291554913</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.001215052992974078</v>
+        <v>0.001197443529307786</v>
       </c>
       <c r="W70">
-        <v>0.2355134905042567</v>
+        <v>0.2355176428157892</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.003573685273453253</v>
+        <v>0.003521892733258203</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.232531643475761</v>
+        <v>0.234431643475761</v>
       </c>
       <c r="C71">
-        <v>-269.6758474065151</v>
+        <v>-281.1354157356768</v>
       </c>
       <c r="D71">
-        <v>228.1021525934849</v>
+        <v>225.8045842643232</v>
       </c>
       <c r="E71">
-        <v>508.278</v>
+        <v>517.4400000000001</v>
       </c>
       <c r="F71">
-        <v>632.178</v>
+        <v>641.34</v>
       </c>
       <c r="G71">
         <v>134.4</v>
@@ -7073,37 +7073,37 @@
         <v>0.525</v>
       </c>
       <c r="M71">
-        <v>149.0675724</v>
+        <v>151.227972</v>
       </c>
       <c r="N71">
-        <v>-148.5425724</v>
+        <v>-150.702972</v>
       </c>
       <c r="O71">
-        <v>-50.50447461600001</v>
+        <v>-51.23901048000001</v>
       </c>
       <c r="P71">
-        <v>-98.038097784</v>
+        <v>-99.46396152</v>
       </c>
       <c r="Q71">
-        <v>-97.97109778400001</v>
+        <v>-99.39696152</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2258853868802143</v>
+        <v>0.2318882331095548</v>
       </c>
       <c r="T71">
-        <v>2.347116291554913</v>
+        <v>2.42535350127341</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.001197443529307786</v>
+        <v>0.001180337193174818</v>
       </c>
       <c r="W71">
-        <v>0.2355176428157892</v>
+        <v>0.2355216764898494</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.003521892733258203</v>
+        <v>0.003471579979925976</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.234431643475761</v>
+        <v>0.236331643475761</v>
       </c>
       <c r="C72">
-        <v>-281.1354157356768</v>
+        <v>-292.5491609170844</v>
       </c>
       <c r="D72">
-        <v>225.8045842643232</v>
+        <v>223.5528390829157</v>
       </c>
       <c r="E72">
-        <v>517.4400000000001</v>
+        <v>526.6020000000001</v>
       </c>
       <c r="F72">
-        <v>641.34</v>
+        <v>650.5020000000001</v>
       </c>
       <c r="G72">
         <v>134.4</v>
@@ -7155,37 +7155,37 @@
         <v>0.525</v>
       </c>
       <c r="M72">
-        <v>151.227972</v>
+        <v>153.3883716</v>
       </c>
       <c r="N72">
-        <v>-150.702972</v>
+        <v>-152.8633716</v>
       </c>
       <c r="O72">
-        <v>-51.23901048000001</v>
+        <v>-51.97354634400001</v>
       </c>
       <c r="P72">
-        <v>-99.46396152</v>
+        <v>-100.889825256</v>
       </c>
       <c r="Q72">
-        <v>-99.39696152</v>
+        <v>-100.822825256</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2318882331095548</v>
+        <v>0.2383050687340222</v>
       </c>
       <c r="T72">
-        <v>2.42535350127341</v>
+        <v>2.508986380627666</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.001180337193174818</v>
+        <v>0.001163712725665314</v>
       </c>
       <c r="W72">
-        <v>0.2355216764898494</v>
+        <v>0.2355255965392881</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.003471579979925976</v>
+        <v>0.003422684487250915</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.236331643475761</v>
+        <v>0.238231643475761</v>
       </c>
       <c r="C73">
-        <v>-292.5491609170843</v>
+        <v>-303.9184402739798</v>
       </c>
       <c r="D73">
-        <v>223.5528390829157</v>
+        <v>221.3455597260201</v>
       </c>
       <c r="E73">
-        <v>526.602</v>
+        <v>535.7639999999999</v>
       </c>
       <c r="F73">
-        <v>650.502</v>
+        <v>659.6639999999999</v>
       </c>
       <c r="G73">
         <v>134.4</v>
@@ -7237,37 +7237,37 @@
         <v>0.525</v>
       </c>
       <c r="M73">
-        <v>153.3883716</v>
+        <v>155.5487712</v>
       </c>
       <c r="N73">
-        <v>-152.8633716</v>
+        <v>-155.0237712</v>
       </c>
       <c r="O73">
-        <v>-51.973546344</v>
+        <v>-52.70808220799999</v>
       </c>
       <c r="P73">
-        <v>-100.889825256</v>
+        <v>-102.315688992</v>
       </c>
       <c r="Q73">
-        <v>-100.822825256</v>
+        <v>-102.248688992</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2383050687340222</v>
+        <v>0.2451802497602372</v>
       </c>
       <c r="T73">
-        <v>2.508986380627666</v>
+        <v>2.598593037078653</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.001163712725665314</v>
+        <v>0.001147550048919962</v>
       </c>
       <c r="W73">
-        <v>0.2355255965392881</v>
+        <v>0.2355294076984647</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.003422684487250915</v>
+        <v>0.003375147202705819</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.238231643475761</v>
+        <v>0.240131643475761</v>
       </c>
       <c r="C74">
-        <v>-303.9184402739798</v>
+        <v>-315.2445580468627</v>
       </c>
       <c r="D74">
-        <v>221.3455597260201</v>
+        <v>219.1814419531372</v>
       </c>
       <c r="E74">
-        <v>535.7639999999999</v>
+        <v>544.9259999999999</v>
       </c>
       <c r="F74">
-        <v>659.6639999999999</v>
+        <v>668.8259999999999</v>
       </c>
       <c r="G74">
         <v>134.4</v>
@@ -7319,37 +7319,37 @@
         <v>0.525</v>
       </c>
       <c r="M74">
-        <v>155.5487712</v>
+        <v>157.7091708</v>
       </c>
       <c r="N74">
-        <v>-155.0237712</v>
+        <v>-157.1841708</v>
       </c>
       <c r="O74">
-        <v>-52.70808220799999</v>
+        <v>-53.44261807199999</v>
       </c>
       <c r="P74">
-        <v>-102.315688992</v>
+        <v>-103.741552728</v>
       </c>
       <c r="Q74">
-        <v>-102.248688992</v>
+        <v>-103.674552728</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2451802497602372</v>
+        <v>0.2525647034550608</v>
       </c>
       <c r="T74">
-        <v>2.598593037078653</v>
+        <v>2.694837223637122</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.001147550048919962</v>
+        <v>0.001131830185236127</v>
       </c>
       <c r="W74">
-        <v>0.2355294076984647</v>
+        <v>0.2355331144423213</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.003375147202705819</v>
+        <v>0.00332891230951804</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.240131643475761</v>
+        <v>0.242031643475761</v>
       </c>
       <c r="C75">
-        <v>-315.2445580468627</v>
+        <v>-326.5287679633404</v>
       </c>
       <c r="D75">
-        <v>219.1814419531372</v>
+        <v>217.0592320366595</v>
       </c>
       <c r="E75">
-        <v>544.9259999999999</v>
+        <v>554.088</v>
       </c>
       <c r="F75">
-        <v>668.8259999999999</v>
+        <v>677.9879999999999</v>
       </c>
       <c r="G75">
         <v>134.4</v>
@@ -7401,37 +7401,37 @@
         <v>0.525</v>
       </c>
       <c r="M75">
-        <v>157.7091708</v>
+        <v>159.8695704</v>
       </c>
       <c r="N75">
-        <v>-157.1841708</v>
+        <v>-159.3445704</v>
       </c>
       <c r="O75">
-        <v>-53.44261807199999</v>
+        <v>-54.177153936</v>
       </c>
       <c r="P75">
-        <v>-103.741552728</v>
+        <v>-105.167416464</v>
       </c>
       <c r="Q75">
-        <v>-103.674552728</v>
+        <v>-105.100416464</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2525647034550608</v>
+        <v>0.2605171920494863</v>
       </c>
       <c r="T75">
-        <v>2.694837223637122</v>
+        <v>2.798484809161627</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.001131830185236127</v>
+        <v>0.001116535182732936</v>
       </c>
       <c r="W75">
-        <v>0.2355331144423213</v>
+        <v>0.2355367210039116</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.00332891230951804</v>
+        <v>0.003283927008038035</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.242031643475761</v>
+        <v>0.243931643475761</v>
       </c>
       <c r="C76">
-        <v>-326.5287679633404</v>
+        <v>-337.7722756601163</v>
       </c>
       <c r="D76">
-        <v>217.0592320366595</v>
+        <v>214.9777243398837</v>
       </c>
       <c r="E76">
-        <v>554.088</v>
+        <v>563.25</v>
       </c>
       <c r="F76">
-        <v>677.9879999999999</v>
+        <v>687.15</v>
       </c>
       <c r="G76">
         <v>134.4</v>
@@ -7483,37 +7483,37 @@
         <v>0.525</v>
       </c>
       <c r="M76">
-        <v>159.8695704</v>
+        <v>162.02997</v>
       </c>
       <c r="N76">
-        <v>-159.3445704</v>
+        <v>-161.50497</v>
       </c>
       <c r="O76">
-        <v>-54.177153936</v>
+        <v>-54.9116898</v>
       </c>
       <c r="P76">
-        <v>-105.167416464</v>
+        <v>-106.5932802</v>
       </c>
       <c r="Q76">
-        <v>-105.100416464</v>
+        <v>-106.5262802</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2605171920494863</v>
+        <v>0.2691058797314657</v>
       </c>
       <c r="T76">
-        <v>2.798484809161627</v>
+        <v>2.910424201528092</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.001116535182732936</v>
+        <v>0.001101648046963164</v>
       </c>
       <c r="W76">
-        <v>0.2355367210039116</v>
+        <v>0.2355402313905261</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.003283927008038035</v>
+        <v>0.0032401413145976</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.243931643475761</v>
+        <v>0.245831643475761</v>
       </c>
       <c r="C77">
-        <v>-337.7722756601163</v>
+        <v>-348.9762409669468</v>
       </c>
       <c r="D77">
-        <v>214.9777243398837</v>
+        <v>212.9357590330532</v>
       </c>
       <c r="E77">
-        <v>563.25</v>
+        <v>572.412</v>
       </c>
       <c r="F77">
-        <v>687.15</v>
+        <v>696.312</v>
       </c>
       <c r="G77">
         <v>134.4</v>
@@ -7565,37 +7565,37 @@
         <v>0.525</v>
       </c>
       <c r="M77">
-        <v>162.02997</v>
+        <v>164.1903696</v>
       </c>
       <c r="N77">
-        <v>-161.50497</v>
+        <v>-163.6653696</v>
       </c>
       <c r="O77">
-        <v>-54.9116898</v>
+        <v>-55.646225664</v>
       </c>
       <c r="P77">
-        <v>-106.5932802</v>
+        <v>-108.019143936</v>
       </c>
       <c r="Q77">
-        <v>-106.5262802</v>
+        <v>-107.952143936</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2691058797314657</v>
+        <v>0.2784102913869435</v>
       </c>
       <c r="T77">
-        <v>2.910424201528092</v>
+        <v>3.031691876591763</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.001101648046963164</v>
+        <v>0.001087152677924175</v>
       </c>
       <c r="W77">
-        <v>0.2355402313905261</v>
+        <v>0.2355436493985455</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.0032401413145976</v>
+        <v>0.003197507876247618</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.245831643475761</v>
+        <v>0.247731643475761</v>
       </c>
       <c r="C78">
-        <v>-348.9762409669468</v>
+        <v>-360.1417800616571</v>
       </c>
       <c r="D78">
-        <v>212.9357590330532</v>
+        <v>210.9322199383428</v>
       </c>
       <c r="E78">
-        <v>572.412</v>
+        <v>581.574</v>
       </c>
       <c r="F78">
-        <v>696.312</v>
+        <v>705.4739999999999</v>
       </c>
       <c r="G78">
         <v>134.4</v>
@@ -7647,37 +7647,37 @@
         <v>0.525</v>
       </c>
       <c r="M78">
-        <v>164.1903696</v>
+        <v>166.3507692</v>
       </c>
       <c r="N78">
-        <v>-163.6653696</v>
+        <v>-165.8257692</v>
       </c>
       <c r="O78">
-        <v>-55.646225664</v>
+        <v>-56.380761528</v>
       </c>
       <c r="P78">
-        <v>-108.019143936</v>
+        <v>-109.445007672</v>
       </c>
       <c r="Q78">
-        <v>-107.952143936</v>
+        <v>-109.378007672</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2784102913869435</v>
+        <v>0.2885237823168106</v>
       </c>
       <c r="T78">
-        <v>3.031691876591763</v>
+        <v>3.163504566878361</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.001087152677924175</v>
+        <v>0.001073033811977108</v>
       </c>
       <c r="W78">
-        <v>0.2355436493985455</v>
+        <v>0.2355469786271358</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.003197507876247618</v>
+        <v>0.003155981799932706</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.247731643475761</v>
+        <v>0.249631643475761</v>
       </c>
       <c r="C79">
-        <v>-360.1417800616571</v>
+        <v>-371.2699675046313</v>
       </c>
       <c r="D79">
-        <v>210.9322199383428</v>
+        <v>208.9660324953686</v>
       </c>
       <c r="E79">
-        <v>581.574</v>
+        <v>590.736</v>
       </c>
       <c r="F79">
-        <v>705.4739999999999</v>
+        <v>714.636</v>
       </c>
       <c r="G79">
         <v>134.4</v>
@@ -7729,37 +7729,37 @@
         <v>0.525</v>
       </c>
       <c r="M79">
-        <v>166.3507692</v>
+        <v>168.5111688</v>
       </c>
       <c r="N79">
-        <v>-165.8257692</v>
+        <v>-167.9861688</v>
       </c>
       <c r="O79">
-        <v>-56.380761528</v>
+        <v>-57.115297392</v>
       </c>
       <c r="P79">
-        <v>-109.445007672</v>
+        <v>-110.870871408</v>
       </c>
       <c r="Q79">
-        <v>-109.378007672</v>
+        <v>-110.803871408</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2885237823168106</v>
+        <v>0.2995566815130292</v>
       </c>
       <c r="T79">
-        <v>3.163504566878361</v>
+        <v>3.307300229009196</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.001073033811977108</v>
+        <v>0.001059276968233811</v>
       </c>
       <c r="W79">
-        <v>0.2355469786271358</v>
+        <v>0.2355502224908905</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.003155981799932706</v>
+        <v>0.003115520494805346</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.249631643475761</v>
+        <v>0.251531643475761</v>
       </c>
       <c r="C80">
-        <v>-371.2699675046313</v>
+        <v>-382.3618381605667</v>
       </c>
       <c r="D80">
-        <v>208.9660324953686</v>
+        <v>207.0361618394334</v>
       </c>
       <c r="E80">
-        <v>590.736</v>
+        <v>599.898</v>
       </c>
       <c r="F80">
-        <v>714.636</v>
+        <v>723.798</v>
       </c>
       <c r="G80">
         <v>134.4</v>
@@ -7811,37 +7811,37 @@
         <v>0.525</v>
       </c>
       <c r="M80">
-        <v>168.5111688</v>
+        <v>170.6715684</v>
       </c>
       <c r="N80">
-        <v>-167.9861688</v>
+        <v>-170.1465684</v>
       </c>
       <c r="O80">
-        <v>-57.115297392</v>
+        <v>-57.849833256</v>
       </c>
       <c r="P80">
-        <v>-110.870871408</v>
+        <v>-112.296735144</v>
       </c>
       <c r="Q80">
-        <v>-110.803871408</v>
+        <v>-112.229735144</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2995566815130292</v>
+        <v>0.3116403330136497</v>
       </c>
       <c r="T80">
-        <v>3.307300229009196</v>
+        <v>3.464790716104872</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.001059276968233811</v>
+        <v>0.001045868399015662</v>
       </c>
       <c r="W80">
-        <v>0.2355502224908905</v>
+        <v>0.2355533842315121</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.003115520494805346</v>
+        <v>0.003076083526516671</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.251531643475761</v>
+        <v>0.253431643475761</v>
       </c>
       <c r="C81">
-        <v>-382.3618381605667</v>
+        <v>-393.4183890147136</v>
       </c>
       <c r="D81">
-        <v>207.0361618394334</v>
+        <v>205.1416109852865</v>
       </c>
       <c r="E81">
-        <v>599.898</v>
+        <v>609.0600000000001</v>
       </c>
       <c r="F81">
-        <v>723.798</v>
+        <v>732.96</v>
       </c>
       <c r="G81">
         <v>134.4</v>
@@ -7893,37 +7893,37 @@
         <v>0.525</v>
       </c>
       <c r="M81">
-        <v>170.6715684</v>
+        <v>172.831968</v>
       </c>
       <c r="N81">
-        <v>-170.1465684</v>
+        <v>-172.306968</v>
       </c>
       <c r="O81">
-        <v>-57.849833256</v>
+        <v>-58.58436912000001</v>
       </c>
       <c r="P81">
-        <v>-112.296735144</v>
+        <v>-113.72259888</v>
       </c>
       <c r="Q81">
-        <v>-112.229735144</v>
+        <v>-113.65559888</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3116403330136497</v>
+        <v>0.3249323496643322</v>
       </c>
       <c r="T81">
-        <v>3.464790716104872</v>
+        <v>3.638030251910115</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.001045868399015662</v>
+        <v>0.001032795044027966</v>
       </c>
       <c r="W81">
-        <v>0.2355533842315121</v>
+        <v>0.2355564669286182</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.003076083526516671</v>
+        <v>0.003037632482435271</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.253431643475761</v>
+        <v>0.255331643475761</v>
       </c>
       <c r="C82">
-        <v>-393.4183890147136</v>
+        <v>-404.4405808903007</v>
       </c>
       <c r="D82">
-        <v>205.1416109852865</v>
+        <v>203.2814191096992</v>
       </c>
       <c r="E82">
-        <v>609.0600000000001</v>
+        <v>618.222</v>
       </c>
       <c r="F82">
-        <v>732.96</v>
+        <v>742.122</v>
       </c>
       <c r="G82">
         <v>134.4</v>
@@ -7975,37 +7975,37 @@
         <v>0.525</v>
       </c>
       <c r="M82">
-        <v>172.831968</v>
+        <v>174.9923676</v>
       </c>
       <c r="N82">
-        <v>-172.306968</v>
+        <v>-174.4673676</v>
       </c>
       <c r="O82">
-        <v>-58.58436912000001</v>
+        <v>-59.318904984</v>
       </c>
       <c r="P82">
-        <v>-113.72259888</v>
+        <v>-115.148462616</v>
       </c>
       <c r="Q82">
-        <v>-113.65559888</v>
+        <v>-115.081462616</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3249323496643322</v>
+        <v>0.339623525962455</v>
       </c>
       <c r="T82">
-        <v>3.638030251910115</v>
+        <v>3.829505528326438</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.001032795044027966</v>
+        <v>0.001020044487928855</v>
       </c>
       <c r="W82">
-        <v>0.2355564669286182</v>
+        <v>0.2355594735097464</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.003037632482435271</v>
+        <v>0.00300013084684958</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.255331643475761</v>
+        <v>0.257231643475761</v>
       </c>
       <c r="C83">
-        <v>-404.4405808903007</v>
+        <v>-415.4293400733588</v>
       </c>
       <c r="D83">
-        <v>203.2814191096992</v>
+        <v>201.4546599266411</v>
       </c>
       <c r="E83">
-        <v>618.222</v>
+        <v>627.384</v>
       </c>
       <c r="F83">
-        <v>742.122</v>
+        <v>751.284</v>
       </c>
       <c r="G83">
         <v>134.4</v>
@@ -8057,37 +8057,37 @@
         <v>0.525</v>
       </c>
       <c r="M83">
-        <v>174.9923676</v>
+        <v>177.1527672</v>
       </c>
       <c r="N83">
-        <v>-174.4673676</v>
+        <v>-176.6277672</v>
       </c>
       <c r="O83">
-        <v>-59.318904984</v>
+        <v>-60.053440848</v>
       </c>
       <c r="P83">
-        <v>-115.148462616</v>
+        <v>-116.574326352</v>
       </c>
       <c r="Q83">
-        <v>-115.081462616</v>
+        <v>-116.507326352</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.339623525962455</v>
+        <v>0.3559470551825913</v>
       </c>
       <c r="T83">
-        <v>3.829505528326438</v>
+        <v>4.042255835455684</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.001020044487928855</v>
+        <v>0.001007604921002894</v>
       </c>
       <c r="W83">
-        <v>0.2355594735097464</v>
+        <v>0.2355624067596275</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.00300013084684958</v>
+        <v>0.002963543885302622</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.257231643475761</v>
+        <v>0.259131643475761</v>
       </c>
       <c r="C84">
-        <v>-415.4293400733588</v>
+        <v>-426.3855598507175</v>
       </c>
       <c r="D84">
-        <v>201.4546599266411</v>
+        <v>199.6604401492825</v>
       </c>
       <c r="E84">
-        <v>627.384</v>
+        <v>636.546</v>
       </c>
       <c r="F84">
-        <v>751.284</v>
+        <v>760.446</v>
       </c>
       <c r="G84">
         <v>134.4</v>
@@ -8139,37 +8139,37 @@
         <v>0.525</v>
       </c>
       <c r="M84">
-        <v>177.1527672</v>
+        <v>179.3131668</v>
       </c>
       <c r="N84">
-        <v>-176.6277672</v>
+        <v>-178.7881668</v>
       </c>
       <c r="O84">
-        <v>-60.053440848</v>
+        <v>-60.787976712</v>
       </c>
       <c r="P84">
-        <v>-116.574326352</v>
+        <v>-118.000190088</v>
       </c>
       <c r="Q84">
-        <v>-116.507326352</v>
+        <v>-117.933190088</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3559470551825913</v>
+        <v>0.3741909996050968</v>
       </c>
       <c r="T84">
-        <v>4.042255835455684</v>
+        <v>4.28003559048249</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.001007604921002894</v>
+        <v>0.0009954651026775577</v>
       </c>
       <c r="W84">
-        <v>0.2355624067596275</v>
+        <v>0.2355652693287886</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.002963543885302622</v>
+        <v>0.002927838537286953</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.259131643475761</v>
+        <v>0.261031643475761</v>
       </c>
       <c r="C85">
-        <v>-426.3855598507175</v>
+        <v>-437.3101019665397</v>
       </c>
       <c r="D85">
-        <v>199.6604401492825</v>
+        <v>197.8978980334604</v>
       </c>
       <c r="E85">
-        <v>636.546</v>
+        <v>645.7080000000001</v>
       </c>
       <c r="F85">
-        <v>760.446</v>
+        <v>769.6080000000001</v>
       </c>
       <c r="G85">
         <v>134.4</v>
@@ -8221,37 +8221,37 @@
         <v>0.525</v>
       </c>
       <c r="M85">
-        <v>179.3131668</v>
+        <v>181.4735664</v>
       </c>
       <c r="N85">
-        <v>-178.7881668</v>
+        <v>-180.9485664</v>
       </c>
       <c r="O85">
-        <v>-60.787976712</v>
+        <v>-61.522512576</v>
       </c>
       <c r="P85">
-        <v>-118.000190088</v>
+        <v>-119.426053824</v>
       </c>
       <c r="Q85">
-        <v>-117.933190088</v>
+        <v>-119.359053824</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3741909996050968</v>
+        <v>0.3947154370804154</v>
       </c>
       <c r="T85">
-        <v>4.28003559048249</v>
+        <v>4.547537814887646</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0009954651026775577</v>
+        <v>0.0009836143276456819</v>
       </c>
       <c r="W85">
-        <v>0.2355652693287886</v>
+        <v>0.2355680637415412</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.002927838537286953</v>
+        <v>0.002892983316604925</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.261031643475761</v>
+        <v>0.262931643475761</v>
       </c>
       <c r="C86">
-        <v>-437.3101019665395</v>
+        <v>-448.2037980023848</v>
       </c>
       <c r="D86">
-        <v>197.8978980334605</v>
+        <v>196.166201997615</v>
       </c>
       <c r="E86">
-        <v>645.708</v>
+        <v>654.8699999999999</v>
       </c>
       <c r="F86">
-        <v>769.6079999999999</v>
+        <v>778.7699999999999</v>
       </c>
       <c r="G86">
         <v>134.4</v>
@@ -8303,37 +8303,37 @@
         <v>0.525</v>
       </c>
       <c r="M86">
-        <v>181.4735664</v>
+        <v>183.633966</v>
       </c>
       <c r="N86">
-        <v>-180.9485664</v>
+        <v>-183.108966</v>
       </c>
       <c r="O86">
-        <v>-61.522512576</v>
+        <v>-62.25704844</v>
       </c>
       <c r="P86">
-        <v>-119.426053824</v>
+        <v>-120.85191756</v>
       </c>
       <c r="Q86">
-        <v>-119.359053824</v>
+        <v>-120.78491756</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3947154370804151</v>
+        <v>0.4179764662191095</v>
       </c>
       <c r="T86">
-        <v>4.547537814887643</v>
+        <v>4.85070700254682</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0009836143276456821</v>
+        <v>0.0009720423943792623</v>
       </c>
       <c r="W86">
-        <v>0.2355680637415412</v>
+        <v>0.2355707924034054</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.002892983316604925</v>
+        <v>0.002858948218762536</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.262931643475761</v>
+        <v>0.264831643475761</v>
       </c>
       <c r="C87">
-        <v>-448.2037980023848</v>
+        <v>-459.0674506854444</v>
       </c>
       <c r="D87">
-        <v>196.166201997615</v>
+        <v>194.4645493145555</v>
       </c>
       <c r="E87">
-        <v>654.8699999999999</v>
+        <v>664.0319999999999</v>
       </c>
       <c r="F87">
-        <v>778.7699999999999</v>
+        <v>787.9319999999999</v>
       </c>
       <c r="G87">
         <v>134.4</v>
@@ -8385,37 +8385,37 @@
         <v>0.525</v>
       </c>
       <c r="M87">
-        <v>183.633966</v>
+        <v>185.7943656</v>
       </c>
       <c r="N87">
-        <v>-183.108966</v>
+        <v>-185.2693656</v>
       </c>
       <c r="O87">
-        <v>-62.25704844</v>
+        <v>-62.991584304</v>
       </c>
       <c r="P87">
-        <v>-120.85191756</v>
+        <v>-122.277781296</v>
       </c>
       <c r="Q87">
-        <v>-120.78491756</v>
+        <v>-122.210781296</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4179764662191095</v>
+        <v>0.4445604995204744</v>
       </c>
       <c r="T87">
-        <v>4.85070700254682</v>
+        <v>5.197186074157306</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0009720423943792623</v>
+        <v>0.0009607395758399684</v>
       </c>
       <c r="W87">
-        <v>0.2355707924034054</v>
+        <v>0.235573457608017</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.002858948218762536</v>
+        <v>0.002825704634823456</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.264831643475761</v>
+        <v>0.266731643475761</v>
       </c>
       <c r="C88">
-        <v>-459.0674506854444</v>
+        <v>-469.9018351292699</v>
       </c>
       <c r="D88">
-        <v>194.4645493145555</v>
+        <v>192.7921648707301</v>
       </c>
       <c r="E88">
-        <v>664.0319999999999</v>
+        <v>673.194</v>
       </c>
       <c r="F88">
-        <v>787.9319999999999</v>
+        <v>797.0939999999999</v>
       </c>
       <c r="G88">
         <v>134.4</v>
@@ -8467,37 +8467,37 @@
         <v>0.525</v>
       </c>
       <c r="M88">
-        <v>185.7943656</v>
+        <v>187.9547652</v>
       </c>
       <c r="N88">
-        <v>-185.2693656</v>
+        <v>-187.4297652</v>
       </c>
       <c r="O88">
-        <v>-62.991584304</v>
+        <v>-63.726120168</v>
       </c>
       <c r="P88">
-        <v>-122.277781296</v>
+        <v>-123.703645032</v>
       </c>
       <c r="Q88">
-        <v>-122.210781296</v>
+        <v>-123.636645032</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4445604995204744</v>
+        <v>0.4752343840989725</v>
       </c>
       <c r="T88">
-        <v>5.197186074157306</v>
+        <v>5.596969618323254</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0009607395758399684</v>
+        <v>0.0009496965922096241</v>
       </c>
       <c r="W88">
-        <v>0.235573457608017</v>
+        <v>0.235576061543557</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.002825704634823456</v>
+        <v>0.002793225271204847</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.266731643475761</v>
+        <v>0.268631643475761</v>
       </c>
       <c r="C89">
-        <v>-469.9018351292699</v>
+        <v>-480.7077000110287</v>
       </c>
       <c r="D89">
-        <v>192.7921648707301</v>
+        <v>191.1482999889713</v>
       </c>
       <c r="E89">
-        <v>673.194</v>
+        <v>682.356</v>
       </c>
       <c r="F89">
-        <v>797.0939999999999</v>
+        <v>806.256</v>
       </c>
       <c r="G89">
         <v>134.4</v>
@@ -8549,37 +8549,37 @@
         <v>0.525</v>
       </c>
       <c r="M89">
-        <v>187.9547652</v>
+        <v>190.1151648</v>
       </c>
       <c r="N89">
-        <v>-187.4297652</v>
+        <v>-189.5901648</v>
       </c>
       <c r="O89">
-        <v>-63.726120168</v>
+        <v>-64.460656032</v>
       </c>
       <c r="P89">
-        <v>-123.703645032</v>
+        <v>-125.129508768</v>
       </c>
       <c r="Q89">
-        <v>-123.636645032</v>
+        <v>-125.062508768</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4752343840989725</v>
+        <v>0.5110205827738868</v>
       </c>
       <c r="T89">
-        <v>5.596969618323254</v>
+        <v>6.063383753183525</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0009496965922096241</v>
+        <v>0.000938904585479969</v>
       </c>
       <c r="W89">
-        <v>0.235576061543557</v>
+        <v>0.2355786062987438</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.002793225271204847</v>
+        <v>0.002761484074941145</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.268631643475761</v>
+        <v>0.270531643475761</v>
       </c>
       <c r="C90">
-        <v>-480.7077000110287</v>
+        <v>-491.4857686890394</v>
       </c>
       <c r="D90">
-        <v>191.1482999889713</v>
+        <v>189.5322313109606</v>
       </c>
       <c r="E90">
-        <v>682.356</v>
+        <v>691.518</v>
       </c>
       <c r="F90">
-        <v>806.256</v>
+        <v>815.418</v>
       </c>
       <c r="G90">
         <v>134.4</v>
@@ -8631,37 +8631,37 @@
         <v>0.525</v>
       </c>
       <c r="M90">
-        <v>190.1151648</v>
+        <v>192.2755644</v>
       </c>
       <c r="N90">
-        <v>-189.5901648</v>
+        <v>-191.7505644</v>
       </c>
       <c r="O90">
-        <v>-64.460656032</v>
+        <v>-65.19519189600001</v>
       </c>
       <c r="P90">
-        <v>-125.129508768</v>
+        <v>-126.555372504</v>
       </c>
       <c r="Q90">
-        <v>-125.062508768</v>
+        <v>-126.488372504</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5110205827738868</v>
+        <v>0.5533133630260584</v>
       </c>
       <c r="T90">
-        <v>6.063383753183525</v>
+        <v>6.614600458018391</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.000938904585479969</v>
+        <v>0.000928355095755475</v>
       </c>
       <c r="W90">
-        <v>0.2355786062987438</v>
+        <v>0.2355810938684209</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.002761484074941145</v>
+        <v>0.002730456163986705</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.270531643475761</v>
+        <v>0.272431643475761</v>
       </c>
       <c r="C91">
-        <v>-491.4857686890394</v>
+        <v>-502.2367402640936</v>
       </c>
       <c r="D91">
-        <v>189.5322313109606</v>
+        <v>187.9432597359063</v>
       </c>
       <c r="E91">
-        <v>691.518</v>
+        <v>700.6799999999999</v>
       </c>
       <c r="F91">
-        <v>815.418</v>
+        <v>824.5799999999999</v>
       </c>
       <c r="G91">
         <v>134.4</v>
@@ -8713,37 +8713,37 @@
         <v>0.525</v>
       </c>
       <c r="M91">
-        <v>192.2755644</v>
+        <v>194.435964</v>
       </c>
       <c r="N91">
-        <v>-191.7505644</v>
+        <v>-193.910964</v>
       </c>
       <c r="O91">
-        <v>-65.19519189600001</v>
+        <v>-65.92972775999999</v>
       </c>
       <c r="P91">
-        <v>-126.555372504</v>
+        <v>-127.98123624</v>
       </c>
       <c r="Q91">
-        <v>-126.488372504</v>
+        <v>-127.91423624</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5533133630260584</v>
+        <v>0.6040646993286642</v>
       </c>
       <c r="T91">
-        <v>6.614600458018391</v>
+        <v>7.27606050382023</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.000928355095755475</v>
+        <v>0.0009180400391359699</v>
       </c>
       <c r="W91">
-        <v>0.2355810938684209</v>
+        <v>0.2355835261587717</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.002730456163986705</v>
+        <v>0.002700117762164611</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.272431643475761</v>
+        <v>0.274331643475761</v>
       </c>
       <c r="C92">
-        <v>-502.2367402640936</v>
+        <v>-512.9612905878352</v>
       </c>
       <c r="D92">
-        <v>187.9432597359063</v>
+        <v>186.3807094121648</v>
       </c>
       <c r="E92">
-        <v>700.6799999999999</v>
+        <v>709.842</v>
       </c>
       <c r="F92">
-        <v>824.5799999999999</v>
+        <v>833.742</v>
       </c>
       <c r="G92">
         <v>134.4</v>
@@ -8795,37 +8795,37 @@
         <v>0.525</v>
       </c>
       <c r="M92">
-        <v>194.435964</v>
+        <v>196.5963636</v>
       </c>
       <c r="N92">
-        <v>-193.910964</v>
+        <v>-196.0713636</v>
       </c>
       <c r="O92">
-        <v>-65.92972775999999</v>
+        <v>-66.664263624</v>
       </c>
       <c r="P92">
-        <v>-127.98123624</v>
+        <v>-129.407099976</v>
       </c>
       <c r="Q92">
-        <v>-127.91423624</v>
+        <v>-129.340099976</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6040646993286642</v>
+        <v>0.6660941103651826</v>
       </c>
       <c r="T92">
-        <v>7.27606050382023</v>
+        <v>8.084511670911368</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0009180400391359699</v>
+        <v>0.0009079516870575526</v>
       </c>
       <c r="W92">
-        <v>0.2355835261587717</v>
+        <v>0.2355859049921918</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.002700117762164611</v>
+        <v>0.002670446138404614</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.274331643475761</v>
+        <v>0.276231643475761</v>
       </c>
       <c r="C93">
-        <v>-512.9612905878352</v>
+        <v>-523.6600732212514</v>
       </c>
       <c r="D93">
-        <v>186.3807094121648</v>
+        <v>184.8439267787485</v>
       </c>
       <c r="E93">
-        <v>709.842</v>
+        <v>719.004</v>
       </c>
       <c r="F93">
-        <v>833.742</v>
+        <v>842.904</v>
       </c>
       <c r="G93">
         <v>134.4</v>
@@ -8877,37 +8877,37 @@
         <v>0.525</v>
       </c>
       <c r="M93">
-        <v>196.5963636</v>
+        <v>198.7567632</v>
       </c>
       <c r="N93">
-        <v>-196.0713636</v>
+        <v>-198.2317632</v>
       </c>
       <c r="O93">
-        <v>-66.664263624</v>
+        <v>-67.39879948799999</v>
       </c>
       <c r="P93">
-        <v>-129.407099976</v>
+        <v>-130.832963712</v>
       </c>
       <c r="Q93">
-        <v>-129.340099976</v>
+        <v>-130.765963712</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6660941103651826</v>
+        <v>0.7436308741608307</v>
       </c>
       <c r="T93">
-        <v>8.084511670911368</v>
+        <v>9.095075629775293</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0009079516870575526</v>
+        <v>0.00089808264698084</v>
       </c>
       <c r="W93">
-        <v>0.2355859049921918</v>
+        <v>0.2355882321118419</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.002670446138404614</v>
+        <v>0.00264141954994368</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.276231643475761</v>
+        <v>0.278131643475761</v>
       </c>
       <c r="C94">
-        <v>-523.6600732212514</v>
+        <v>-534.3337203461351</v>
       </c>
       <c r="D94">
-        <v>184.8439267787485</v>
+        <v>183.3322796538649</v>
       </c>
       <c r="E94">
-        <v>719.004</v>
+        <v>728.1660000000001</v>
       </c>
       <c r="F94">
-        <v>842.904</v>
+        <v>852.066</v>
       </c>
       <c r="G94">
         <v>134.4</v>
@@ -8959,37 +8959,37 @@
         <v>0.525</v>
       </c>
       <c r="M94">
-        <v>198.7567632</v>
+        <v>200.9171628</v>
       </c>
       <c r="N94">
-        <v>-198.2317632</v>
+        <v>-200.3921628</v>
       </c>
       <c r="O94">
-        <v>-67.39879948799999</v>
+        <v>-68.13333535200002</v>
       </c>
       <c r="P94">
-        <v>-130.832963712</v>
+        <v>-132.258827448</v>
       </c>
       <c r="Q94">
-        <v>-130.765963712</v>
+        <v>-132.191827448</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7436308741608307</v>
+        <v>0.8433209990409495</v>
       </c>
       <c r="T94">
-        <v>9.095075629775293</v>
+        <v>10.39437214831462</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.00089808264698084</v>
+        <v>0.0008884258443251319</v>
       </c>
       <c r="W94">
-        <v>0.2355882321118419</v>
+        <v>0.2355905091859082</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.00264141954994368</v>
+        <v>0.002613017189191602</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.278131643475761</v>
+        <v>0.280031643475761</v>
       </c>
       <c r="C95">
-        <v>-534.3337203461351</v>
+        <v>-544.9828436321841</v>
       </c>
       <c r="D95">
-        <v>183.3322796538649</v>
+        <v>181.8451563678159</v>
       </c>
       <c r="E95">
-        <v>728.1660000000001</v>
+        <v>737.328</v>
       </c>
       <c r="F95">
-        <v>852.066</v>
+        <v>861.228</v>
       </c>
       <c r="G95">
         <v>134.4</v>
@@ -9041,37 +9041,37 @@
         <v>0.525</v>
       </c>
       <c r="M95">
-        <v>200.9171628</v>
+        <v>203.0775624</v>
       </c>
       <c r="N95">
-        <v>-200.3921628</v>
+        <v>-202.5525624</v>
       </c>
       <c r="O95">
-        <v>-68.13333535200002</v>
+        <v>-68.86787121600001</v>
       </c>
       <c r="P95">
-        <v>-132.258827448</v>
+        <v>-133.684691184</v>
       </c>
       <c r="Q95">
-        <v>-132.191827448</v>
+        <v>-133.617691184</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8433209990409495</v>
+        <v>0.9762411655477744</v>
       </c>
       <c r="T95">
-        <v>10.39437214831462</v>
+        <v>12.12676750636706</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.0008884258443251319</v>
+        <v>0.0008789745055557157</v>
       </c>
       <c r="W95">
-        <v>0.2355905091859082</v>
+        <v>0.23559273781159</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.002613017189191602</v>
+        <v>0.00258521913398746</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.280031643475761</v>
+        <v>0.281931643475761</v>
       </c>
       <c r="C96">
-        <v>-544.9828436321841</v>
+        <v>-555.6080350622404</v>
       </c>
       <c r="D96">
-        <v>181.8451563678159</v>
+        <v>180.3819649377596</v>
       </c>
       <c r="E96">
-        <v>737.328</v>
+        <v>746.49</v>
       </c>
       <c r="F96">
-        <v>861.228</v>
+        <v>870.39</v>
       </c>
       <c r="G96">
         <v>134.4</v>
@@ -9123,37 +9123,37 @@
         <v>0.525</v>
       </c>
       <c r="M96">
-        <v>203.0775624</v>
+        <v>205.237962</v>
       </c>
       <c r="N96">
-        <v>-202.5525624</v>
+        <v>-204.712962</v>
       </c>
       <c r="O96">
-        <v>-68.86787121600001</v>
+        <v>-69.60240708000001</v>
       </c>
       <c r="P96">
-        <v>-133.684691184</v>
+        <v>-135.11055492</v>
       </c>
       <c r="Q96">
-        <v>-133.617691184</v>
+        <v>-135.04355492</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9762411655477744</v>
+        <v>1.16232939865733</v>
       </c>
       <c r="T96">
-        <v>12.12676750636706</v>
+        <v>14.55212100764048</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0008789745055557157</v>
+        <v>0.0008697221423393397</v>
       </c>
       <c r="W96">
-        <v>0.23559273781159</v>
+        <v>0.2355949195188364</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.00258521913398746</v>
+        <v>0.002558006300998117</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.281931643475761</v>
+        <v>0.283831643475761</v>
       </c>
       <c r="C97">
-        <v>-555.6080350622404</v>
+        <v>-566.2098677180052</v>
       </c>
       <c r="D97">
-        <v>180.3819649377596</v>
+        <v>178.9421322819948</v>
       </c>
       <c r="E97">
-        <v>746.49</v>
+        <v>755.652</v>
       </c>
       <c r="F97">
-        <v>870.39</v>
+        <v>879.552</v>
       </c>
       <c r="G97">
         <v>134.4</v>
@@ -9205,37 +9205,37 @@
         <v>0.525</v>
       </c>
       <c r="M97">
-        <v>205.237962</v>
+        <v>207.3983616</v>
       </c>
       <c r="N97">
-        <v>-204.712962</v>
+        <v>-206.8733616</v>
       </c>
       <c r="O97">
-        <v>-69.60240708000001</v>
+        <v>-70.33694294400001</v>
       </c>
       <c r="P97">
-        <v>-135.11055492</v>
+        <v>-136.536418656</v>
       </c>
       <c r="Q97">
-        <v>-135.04355492</v>
+        <v>-136.469418656</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.16232939865733</v>
+        <v>1.441461748321663</v>
       </c>
       <c r="T97">
-        <v>14.55212100764048</v>
+        <v>18.19015125955061</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0008697221423393397</v>
+        <v>0.0008606625366899716</v>
       </c>
       <c r="W97">
-        <v>0.2355949195188364</v>
+        <v>0.2355970557738485</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.002558006300998117</v>
+        <v>0.002531360402029392</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.283831643475761</v>
+        <v>0.285731643475761</v>
       </c>
       <c r="C98">
-        <v>-566.2098677180052</v>
+        <v>-576.7888965284219</v>
       </c>
       <c r="D98">
-        <v>178.9421322819948</v>
+        <v>177.5251034715781</v>
       </c>
       <c r="E98">
-        <v>755.6519999999999</v>
+        <v>764.814</v>
       </c>
       <c r="F98">
-        <v>879.5519999999999</v>
+        <v>888.7139999999999</v>
       </c>
       <c r="G98">
         <v>134.4</v>
@@ -9287,37 +9287,37 @@
         <v>0.525</v>
       </c>
       <c r="M98">
-        <v>207.3983616</v>
+        <v>209.5587612</v>
       </c>
       <c r="N98">
-        <v>-206.8733616</v>
+        <v>-209.0337612</v>
       </c>
       <c r="O98">
-        <v>-70.336942944</v>
+        <v>-71.07147880799999</v>
       </c>
       <c r="P98">
-        <v>-136.536418656</v>
+        <v>-137.962282392</v>
       </c>
       <c r="Q98">
-        <v>-136.469418656</v>
+        <v>-137.895282392</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.44146174832166</v>
+        <v>1.906682331095546</v>
       </c>
       <c r="T98">
-        <v>18.19015125955056</v>
+        <v>24.25353501273408</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0008606625366899718</v>
+        <v>0.0008517897270333741</v>
       </c>
       <c r="W98">
-        <v>0.2355970557738485</v>
+        <v>0.2355991479823655</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.002531360402029392</v>
+        <v>0.002505263903039401</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.285731643475761</v>
+        <v>0.287631643475761</v>
       </c>
       <c r="C99">
-        <v>-576.7888965284219</v>
+        <v>-587.3456589827811</v>
       </c>
       <c r="D99">
-        <v>177.5251034715781</v>
+        <v>176.1303410172188</v>
       </c>
       <c r="E99">
-        <v>764.814</v>
+        <v>773.9759999999999</v>
       </c>
       <c r="F99">
-        <v>888.7139999999999</v>
+        <v>897.8759999999999</v>
       </c>
       <c r="G99">
         <v>134.4</v>
@@ -9369,37 +9369,37 @@
         <v>0.525</v>
       </c>
       <c r="M99">
-        <v>209.5587612</v>
+        <v>211.7191608</v>
       </c>
       <c r="N99">
-        <v>-209.0337612</v>
+        <v>-211.1941608</v>
       </c>
       <c r="O99">
-        <v>-71.07147880799999</v>
+        <v>-71.80601467199999</v>
       </c>
       <c r="P99">
-        <v>-137.962282392</v>
+        <v>-139.388146128</v>
       </c>
       <c r="Q99">
-        <v>-137.895282392</v>
+        <v>-139.321146128</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.906682331095546</v>
+        <v>2.837123496643319</v>
       </c>
       <c r="T99">
-        <v>24.25353501273408</v>
+        <v>36.38030251910112</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0008517897270333741</v>
+        <v>0.0008430979951248704</v>
       </c>
       <c r="W99">
-        <v>0.2355991479823655</v>
+        <v>0.2356011974927496</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.002505263903039401</v>
+        <v>0.002479699985661443</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.287631643475761</v>
+        <v>0.289531643475761</v>
       </c>
       <c r="C100">
-        <v>-587.3456589827811</v>
+        <v>-597.880675810471</v>
       </c>
       <c r="D100">
-        <v>176.1303410172188</v>
+        <v>174.7573241895289</v>
       </c>
       <c r="E100">
-        <v>773.9759999999999</v>
+        <v>783.1379999999999</v>
       </c>
       <c r="F100">
-        <v>897.8759999999999</v>
+        <v>907.0379999999999</v>
       </c>
       <c r="G100">
         <v>134.4</v>
@@ -9451,37 +9451,37 @@
         <v>0.525</v>
       </c>
       <c r="M100">
-        <v>211.7191608</v>
+        <v>213.8795604</v>
       </c>
       <c r="N100">
-        <v>-211.1941608</v>
+        <v>-213.3545604</v>
       </c>
       <c r="O100">
-        <v>-71.80601467199999</v>
+        <v>-72.540550536</v>
       </c>
       <c r="P100">
-        <v>-139.388146128</v>
+        <v>-140.814009864</v>
       </c>
       <c r="Q100">
-        <v>-139.321146128</v>
+        <v>-140.7470098639999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.837123496643319</v>
+        <v>5.628446993286638</v>
       </c>
       <c r="T100">
-        <v>36.38030251910112</v>
+        <v>72.76060503820224</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0008430979951248704</v>
+        <v>0.0008345818537599727</v>
       </c>
       <c r="W100">
-        <v>0.2356011974927496</v>
+        <v>0.2356032055988834</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9489,91 +9489,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.002479699985661443</v>
+        <v>0.002454652511058808</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.289531643475761</v>
-      </c>
-      <c r="C101">
-        <v>-597.880675810471</v>
-      </c>
-      <c r="D101">
-        <v>174.7573241895289</v>
-      </c>
-      <c r="E101">
-        <v>783.1379999999999</v>
-      </c>
-      <c r="F101">
-        <v>907.0379999999999</v>
-      </c>
-      <c r="G101">
-        <v>134.4</v>
-      </c>
-      <c r="H101">
-        <v>792.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.592</v>
-      </c>
-      <c r="K101">
-        <v>0.06699999999999998</v>
-      </c>
-      <c r="L101">
-        <v>0.525</v>
-      </c>
-      <c r="M101">
-        <v>213.8795604</v>
-      </c>
-      <c r="N101">
-        <v>-213.3545604</v>
-      </c>
-      <c r="O101">
-        <v>-72.540550536</v>
-      </c>
-      <c r="P101">
-        <v>-140.814009864</v>
-      </c>
-      <c r="Q101">
-        <v>-140.7470098639999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.628446993286638</v>
-      </c>
-      <c r="T101">
-        <v>72.76060503820224</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0008345818537599727</v>
-      </c>
-      <c r="W101">
-        <v>0.2356032055988834</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.002454652511058808</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
